--- a/test/quality_check/output.xlsx
+++ b/test/quality_check/output.xlsx
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 字段中文名'PTP状态标志'中'PTP'为英文缩写，并非常见金融名称，普通读者无法仅凭字段名理解其含义，不属于见名知意。业务含义'PTP状态标志'与字段名完全相同，未提供任何解释或补充信息，因此无效。</t>
+          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 字段中文名'PTP状态标志'中'PTP'为未解释的英文缩写（催收场景中通常指Promise To Pay承诺还款），对一般读者而言无法从名称直接得知其含义，不属于见名知意的常见金融名称，与示例中'CDA规则结果'情况类似。业务含义'PTP状态标志'与字段名完全相同，未提供任何实质解释，故判定为无效。</t>
         </is>
       </c>
     </row>
@@ -1249,14 +1249,10 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="J13" t="inlineStr">
@@ -1301,14 +1297,10 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="J14" t="inlineStr">
@@ -3973,7 +3965,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>字段中文名'模板编号'表示模板的编号，但业务含义'关联参数模板维护功能维护这一条数据的时间'描述的是维护时间，与字段含义完全不符，属于语义错位/描述错误，未对'模板编号'进行任何有效解释，判定为无效。</t>
+          <t>字段中文名'模板编号'表示模板的编号，而业务含义'关联参数模板维护功能维护这一条数据的时间'描述的是维护时间，两者语义完全不一致。业务含义描述的是'时间'属性，与字段名'模板编号'所指的编号属性相矛盾，未对字段进行正确解释，属于无效。</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4109,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>数据示例'一键多属性模板'不符合域类型'an..(30)'的限制: 包含汉字字符'一'（数字+字母+特殊符号类不允许汉字）; 字段中文名'模板类型'表示模板的类型，但业务含义'关联参数模板维护功能，维护关联参数以后，该模板的状态'描述的是模板状态，与字段含义不符，属于语义错位/描述错误，未对'模板类型'进行任何有效解释，判定为无效。</t>
+          <t>数据示例'一键多属性模板'不符合域类型'an..(30)'的限制: 包含汉字字符'一'（数字+字母+特殊符号类不允许汉字）; 字段中文名'模板类型'表示模板的类型，而业务含义'关联参数模板维护功能，维护关联参数以后，该模板的状态'描述的是模板的状态，两者语义不一致。业务含义描述的是'状态'属性，与字段名'模板类型'所指的类型属性相矛盾，未对字段进行正确解释，属于无效。</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4157,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>字段中文名'参数模板归属团队'表示模板归属的团队，但业务含义'关联参数模板维护功能，维护人员通过功能输入的模板类型'描述的是模板类型，与字段含义不符，属于语义错位/描述错误，未对'参数模板归属团队'进行任何有效解释，判定为无效。</t>
+          <t>字段中文名'参数模板归属团队'表示参数模板所属的团队，而业务含义'关联参数模板维护功能，维护人员通过功能输入的模板类型'描述的是模板类型，两者语义不一致。业务含义描述的是'模板类型'，与字段名'归属团队'所指的团队属性相矛盾，未对字段进行正确解释，属于无效。</t>
         </is>
       </c>
     </row>
@@ -5544,14 +5536,10 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr"/>
     </row>
     <row r="107" ht="16.5" customHeight="1" s="26">
       <c r="J107" s="2" t="inlineStr">
@@ -6199,7 +6187,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>字段中文名'总Token数'与业务含义'总的Token数'语义完全等价，业务含义只是在原名称基础上添加了无实质意义的'的'字，未提供任何额外信息，属于简单加词，判定为无效。</t>
+          <t>字段中文名'总Token数'与业务含义'总的Token数'在语义上完全等价，业务含义只是在原名称基础上添加了无实质意义的'的'字，未提供任何额外信息，属于简单加词，判定为无效。</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6239,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>字段中文名'影子模型标志'与业务含义'影子模型判断标志'语义基本等价，业务含义只是在'标志'前添加了'判断'二字，'判断标志'与'标志'表达的是同一含义，未提供实质性的新信息，属于语义重复，判定为无效。</t>
+          <t>字段中文名'影子模型标志'与业务含义'影子模型判断标志'语义基本等价，业务含义只是在原名称基础上添加了'判断'二字，'标志'本身已隐含判断的含义，未提供实质性的额外信息，属于简单加词，判定为无效。</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6515,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
+          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
         </is>
       </c>
     </row>
@@ -6618,14 +6606,10 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr"/>
     </row>
     <row r="131" ht="16.5" customHeight="1" s="26">
       <c r="J131" s="8" t="inlineStr">
@@ -6958,14 +6942,10 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr"/>
     </row>
     <row r="138" ht="16.5" customHeight="1" s="26">
       <c r="J138" s="8" t="inlineStr">
@@ -7154,14 +7134,10 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr"/>
     </row>
     <row r="142" ht="132" customHeight="1" s="26">
       <c r="J142" s="8" t="inlineStr">
@@ -7308,7 +7284,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>字段中文名'预约状态'业务含义'指报表预约的预约状态'，其核心语义与字段名完全等价，只是重复了'预约状态'并添加了'报表'这一限定词，未对'预约状态'的含义、取值或业务背景进行实质解释，属于语义重复，判定为无效。</t>
+          <t>字段中文名'预约状态'业务含义'指报表预约的预约状态'只是在原名称基础上添加了'报表'一词，核心语义仍是'预约状态'，与字段中文名语义等价，属于简单加词/语义重复，未提供实质性的新信息，判定为无效。</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7465,7 @@
       </c>
       <c r="W148" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>01-/</t>
         </is>
       </c>
       <c r="Y148" s="9" t="inlineStr">
@@ -7598,7 +7574,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>域类型'i'格式不合法</t>
+          <t>域类型'i'格式不合法; 字段中文名'成立日单位净值'本身含义清晰（成立日的单位净值），业务含义'产品成立日的单位净值'只是在原名称基础上添加'产品'和'的'，语义上完全等价，未提供任何新信息，属于语义重复，无效。</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7718,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
+          <t>字段中文名'理财产品收益类型'本身含义清晰，业务含义'用于标志理财产品的收益类型'只是在原名称基础上添加'用于标志'和'的'，语义上完全等价，未提供任何新信息，属于语义重复，无效。</t>
         </is>
       </c>
     </row>
@@ -7833,14 +7809,10 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr"/>
     </row>
     <row r="156" ht="16.5" customHeight="1" s="26">
       <c r="J156" s="8" t="inlineStr">
@@ -7963,7 +7935,7 @@
       </c>
       <c r="W158" s="23" t="inlineStr">
         <is>
-          <t>01-【省直分行】对应字典枚举值</t>
+          <t>【省直分行】对应字典枚举值</t>
         </is>
       </c>
       <c r="Y158" s="23" t="inlineStr">
@@ -7973,14 +7945,10 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr"/>
     </row>
     <row r="159" ht="49.5" customHeight="1" s="26">
       <c r="J159" s="8" t="inlineStr">
@@ -8025,14 +7993,10 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr"/>
     </row>
     <row r="160" ht="16.5" customHeight="1" s="26">
       <c r="J160" s="8" t="inlineStr">
@@ -8759,14 +8723,10 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr"/>
     </row>
     <row r="176" ht="16.5" customHeight="1" s="26">
       <c r="J176" s="8" t="inlineStr">
@@ -8899,14 +8859,10 @@
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr"/>
     </row>
     <row r="179" ht="16.5" customHeight="1" s="26">
       <c r="J179" s="8" t="inlineStr">
@@ -9703,14 +9659,10 @@
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr"/>
     </row>
     <row r="197" ht="33" customHeight="1" s="26">
       <c r="J197" s="8" t="inlineStr">
@@ -9755,14 +9707,10 @@
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr"/>
     </row>
     <row r="198" ht="33" customHeight="1" s="26">
       <c r="J198" s="8" t="inlineStr">
@@ -9903,14 +9851,10 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr"/>
     </row>
     <row r="201" ht="33" customHeight="1" s="26">
       <c r="J201" s="9" t="inlineStr">
@@ -10143,14 +10087,10 @@
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr"/>
     </row>
     <row r="206" ht="66" customHeight="1" s="26">
       <c r="J206" s="9" t="inlineStr">
@@ -10779,14 +10719,10 @@
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr"/>
     </row>
     <row r="219" ht="33" customHeight="1" s="26">
       <c r="J219" s="11" t="inlineStr">
@@ -10917,7 +10853,7 @@
       </c>
       <c r="W221" s="11" t="inlineStr">
         <is>
-          <t>0000-“产品到期日”、“产品到期资金到账天数”都一致；0001-仅“产品到期日”对平；0002-仅“产品到期资金到账天数”对平;0003-未核对</t>
+          <t>0000-“产品到期日”、“产品到期资金到账天数”都一致；;0001-仅“产品到期日”对平；;0002-仅“产品到期资金到账天数”对平;0003-未核对</t>
         </is>
       </c>
       <c r="Y221" s="11" t="inlineStr">
@@ -10927,14 +10863,10 @@
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr"/>
     </row>
     <row r="222" ht="33" customHeight="1" s="26">
       <c r="J222" s="11" t="inlineStr">
@@ -10980,7 +10912,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>域类型'i(20.4)'格式不合法; 字段中文名'1001银行存款'为科目代码加名称，不属于见名知意的常见金融名称（'1001'为代码，含义不直观），业务含义与字段中文名完全相同，属于完全复制，未对代码含义或科目用途做任何解释，因此无效。</t>
+          <t>域类型'i(20.4)'格式不合法; 字段中文名'1001银行存款'包含科目代码'1001'，代码部分不具有自解释性，不属于完全见名知意的常见名称。业务含义'1001银行存款'与字段中文名完全相同，属于完全复制，未对代码或字段含义做任何解释，未提供实质信息，无效。</t>
         </is>
       </c>
     </row>
@@ -11028,7 +10960,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>域类型'i(20.4)'格式不合法; 字段中文名'1204.01银行存款应收利息'为科目代码加名称，不属于见名知意的常见金融名称（'1204.01'为代码，含义不直观），业务含义与字段中文名完全相同，属于完全复制，未提供任何实质解释，因此无效。</t>
+          <t>域类型'i(20.4)'格式不合法; 字段中文名'1204.01银行存款应收利息'包含科目代码'1204.01'，代码部分不具有自解释性，不属于完全见名知意的常见名称。业务含义'1204.01银行存款应收利息'与字段中文名完全相同，属于完全复制，未对代码或字段含义做任何解释，未提供实质信息，无效。</t>
         </is>
       </c>
     </row>
@@ -11259,14 +11191,10 @@
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr"/>
     </row>
     <row r="229" ht="49.5" customHeight="1" s="26">
       <c r="J229" s="11" t="inlineStr">
@@ -11311,14 +11239,10 @@
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr"/>
     </row>
     <row r="230" ht="33" customHeight="1" s="26">
       <c r="J230" s="9" t="inlineStr">
@@ -11407,14 +11331,10 @@
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr"/>
     </row>
     <row r="232" ht="49.5" customHeight="1" s="26">
       <c r="J232" s="9" t="inlineStr">
@@ -11459,14 +11379,10 @@
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr"/>
     </row>
     <row r="233" ht="33" customHeight="1" s="26">
       <c r="J233" s="9" t="inlineStr">
@@ -11555,14 +11471,10 @@
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr"/>
     </row>
     <row r="235" ht="33" customHeight="1" s="26">
       <c r="J235" s="9" t="inlineStr">
@@ -11607,14 +11519,10 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr"/>
     </row>
     <row r="236" ht="16.5" customHeight="1" s="26">
       <c r="J236" s="9" t="inlineStr">
@@ -12331,14 +12239,10 @@
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr"/>
     </row>
     <row r="251" ht="16.5" customHeight="1" s="26">
       <c r="J251" s="9" t="inlineStr">
@@ -12427,14 +12331,10 @@
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr"/>
     </row>
     <row r="253" ht="33" customHeight="1" s="26">
       <c r="J253" s="9" t="inlineStr">
@@ -12479,14 +12379,10 @@
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr"/>
     </row>
     <row r="254" ht="16.5" customHeight="1" s="26">
       <c r="J254" s="9" t="inlineStr">
@@ -12575,14 +12471,10 @@
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr"/>
     </row>
     <row r="256" ht="33" customHeight="1" s="26">
       <c r="J256" s="9" t="inlineStr">
@@ -12803,14 +12695,10 @@
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="J261" s="14" t="inlineStr">
@@ -13867,14 +13755,10 @@
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB284" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr"/>
     </row>
     <row r="285" ht="16.5" customHeight="1" s="26">
       <c r="J285" s="15" t="inlineStr">
@@ -13919,14 +13803,10 @@
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB285" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr"/>
     </row>
     <row r="286" ht="33" customHeight="1" s="26">
       <c r="J286" s="15" t="inlineStr">
@@ -14107,14 +13987,10 @@
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB289" t="inlineStr"/>
     </row>
     <row r="290" ht="33" customHeight="1" s="26">
       <c r="J290" s="15" t="inlineStr">
@@ -14599,7 +14475,7 @@
       </c>
       <c r="W300" s="9" t="inlineStr">
         <is>
-          <t>YSQZ-疑似欺诈;CLOR-可关闭状态;CLPD-待销户状态;180L-催收逾期180+（历年）;CLOC-客户销户;SFDJ-司法冻结;VIP-贵宾账户;CLPC-待销卡;180B-催收逾期180+（本年）;HZDJ-坏账冻结;TRQITRIAD-强停;FCBC-催收委托外包/分行（欺诈）;CACA-催收委托外包/分行;CLOF-账户冻结-反欺诈发起;FQZW-资产重组;TRDJTRIAD-冻结;ZCST-正常;CLOP-账户冻结-银行发起;CLSK-催收冻结;CLTS-交易监控冻结;VIPC-催收-VIP</t>
+          <t>YSQZ-疑似欺诈;CLOR-可关闭状态;CLPD-待销户状态;180L-催收逾期180+（历年）;CLOC-客户销户;SFDJ-司法冻结;VIP-贵宾账户;CLPC-待销卡;180B-催收逾期180+（本年）;HZDJ-坏账冻结;TRQI-TRIAD强停;FCBC-催收委托外包/分行（欺诈）;CACA-催收委托外包/分行;CLOF-账户冻结-反欺诈发起;FQZW-资产重组;TRDJ-TRIAD冻结;ZCST-正常;CLOP-账户冻结-银行发起;CLSK-催收冻结;CLTS-交易监控冻结;VIPC-催收-VIP</t>
         </is>
       </c>
       <c r="Y300" s="9" t="inlineStr">
@@ -14609,14 +14485,10 @@
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB300" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB300" t="inlineStr"/>
     </row>
     <row r="301" ht="16.5" customHeight="1" s="26">
       <c r="J301" s="9" t="inlineStr">
@@ -15263,14 +15135,10 @@
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB314" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr"/>
     </row>
     <row r="315" ht="16.5" customHeight="1" s="26">
       <c r="J315" s="9" t="inlineStr">
@@ -15544,7 +15412,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
+          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
         </is>
       </c>
     </row>
@@ -15683,14 +15551,10 @@
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB323" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr"/>
     </row>
     <row r="324" ht="16.5" customHeight="1" s="26">
       <c r="J324" s="9" t="inlineStr">
@@ -16135,14 +15999,10 @@
       </c>
       <c r="AA333" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB333" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr"/>
     </row>
     <row r="334" ht="16.5" customHeight="1" s="26">
       <c r="J334" s="9" t="inlineStr">
@@ -16468,7 +16328,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>域类型'i(20)'不允许用于字段所属类型'文本类'; 字段中文名'上一中心号'与业务含义'上一业务中心'在语义上基本等价，只是将'中心号'换成了'业务中心'的说法，未提供字段名中不存在的实质信息（如中心的定义、用途等），属于语义重复，判定为无效。</t>
+          <t>域类型'i(20)'不允许用于字段所属类型'文本类'</t>
         </is>
       </c>
     </row>
@@ -16878,7 +16738,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>字段中文名'用卡判断标识'不属于见名知意的常见金融名称，业务含义'案件客户用卡判断的标识'只是在原名称基础上添加了'案件客户'和'的'，核心语义仍是'用卡判断的标识'，与字段名语义等价，未解释该标识的具体含义、取值或用途，属于简单加词/语义重复，判定为无效。</t>
+          <t>字段中文名'用卡判断标识'不属于见名知意的常见金融名称，业务含义'案件客户用卡判断的标识'只是在原名称基础上添加了'案件客户'和'的'，语义上与字段名完全等价，未解释该标识的具体含义、取值或用途，属于简单加词/语义重复，判定为无效。</t>
         </is>
       </c>
     </row>
@@ -17323,14 +17183,10 @@
       </c>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB359" t="inlineStr">
-        <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类; 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB359" t="inlineStr"/>
     </row>
     <row r="360" ht="49.5" customHeight="1" s="26">
       <c r="J360" s="9" t="inlineStr">
@@ -19145,14 +19001,10 @@
       </c>
       <c r="AA400" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB400" t="inlineStr">
-        <is>
-          <t>字段中文名'重复对话'本身含义清晰，属于见名知意。业务含义'判断是否是重复对话'只是在原名称基础上添加了'判断是否是'这一无实质信息的表述，语义上与字段名完全等价，未提供任何额外信息，因此判定为无效。</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB400" t="inlineStr"/>
     </row>
     <row r="401" ht="33" customHeight="1" s="26">
       <c r="J401" s="9" t="inlineStr">

--- a/test/quality_check/output.xlsx
+++ b/test/quality_check/output.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB401"/>
+  <dimension ref="A1:AC401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="5" customWidth="1" style="26" min="1" max="1"/>
@@ -770,6 +770,11 @@
           <t>说明</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>所属类型检查结果</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="J3" t="inlineStr">
@@ -815,9 +820,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>域类型'i(8)'不允许用于字段所属类型'编码类'</t>
-        </is>
-      </c>
+          <t>1. 域类型'i(8)'不允许用于字段所属类型'编码类'</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="J4" t="inlineStr">
@@ -863,9 +869,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>域类型'DATE'不允许用于字段所属类型'编码类'</t>
-        </is>
-      </c>
+          <t>1. 域类型'DATE'不允许用于字段所属类型'编码类'</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="J5" t="inlineStr">
@@ -906,9 +913,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>必填字段为空: 业务定义</t>
-        </is>
-      </c>
+          <t>1. 必填字段为空: 业务定义</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="J6" t="inlineStr">
@@ -943,7 +951,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1-是;0否</t>
+          <t>1-是;0-否</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -953,14 +961,11 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="J7" t="inlineStr">
@@ -995,7 +1000,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1-是;0否</t>
+          <t>1-是;0-否</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1010,9 +1015,11 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>'是否枚举'为'否'但枚举值不为空</t>
-        </is>
-      </c>
+          <t>1. 标志类字段的'是否枚举'必须为'是'，实际为'否'
+2. '是否枚举'为'否'但枚举值不为空</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="J8" t="inlineStr">
@@ -1047,7 +1054,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1-是;0否</t>
+          <t>1-是;0-否</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1057,14 +1064,11 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an..(2)'不允许用于字段所属类型'标志类'</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="J9" t="inlineStr">
@@ -1099,7 +1103,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1-是;0否</t>
+          <t>1-是;0-否</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1114,9 +1118,10 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 字段中文名'PTP状态标志'中'PTP'为未解释的英文缩写（催收场景中通常指Promise To Pay承诺还款），对一般读者而言无法从名称直接得知其含义，不属于见名知意的常见金融名称，与示例中'CDA规则结果'情况类似。业务含义'PTP状态标志'与字段名完全相同，未提供任何实质解释，故判定为无效。</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'PTP状态标志'中'PTP'为英文缩写（通常指Promise To Pay），对不熟悉该缩写的使用者而言含义不明确，字段名本身不足以见名知意，类似于示例中'CDA规则结果'不属于常见且自明的名称。而业务含义'PTP状态标志'与字段中文名完全复制，未对PTP含义或状态标志的具体内容做任何解释，未提供实质信息，因此判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="J10" t="inlineStr">
@@ -1161,6 +1166,7 @@
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="J11" t="inlineStr">
@@ -1205,6 +1211,7 @@
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="J12" t="inlineStr">
@@ -1253,6 +1260,7 @@
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="J13" t="inlineStr">
@@ -1301,6 +1309,7 @@
         </is>
       </c>
       <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="J14" t="inlineStr">
@@ -1341,9 +1350,10 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>必填字段为空: 业务定义</t>
-        </is>
-      </c>
+          <t>1. 必填字段为空: 业务定义</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="J15" t="inlineStr">
@@ -1378,7 +1388,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1-是;0否</t>
+          <t>1-是;0-否</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -1388,14 +1398,11 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'VARCHAR(1)'格式不合法</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="O16" t="inlineStr">
@@ -1425,7 +1432,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1-是;0否</t>
+          <t>1-是;0-否</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -1440,9 +1447,10 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>必填字段为空: 中文表名; 非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an(10)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 必填字段为空: 中文表名</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="J17" t="inlineStr">
@@ -1488,9 +1496,10 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>域类型'VARCHAR(4)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'VARCHAR(4)'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="J18" t="inlineStr">
@@ -1536,9 +1545,10 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>域类型'DECIMAL(15,2)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'DECIMAL(15,2)'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="J19" t="inlineStr">
@@ -1584,9 +1594,11 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>域类型'i'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'i'格式不合法
+2. 字段中文名'外包手次'中的'手次'是催收行业的专业术语（指委外催收的轮次/次数），并非常见金融名称，字段名本身不易被直观理解，不属于见名知意。业务含义只是原样复制字段名，未对'手次'的含义做任何解释，未提供实质信息，因此无效。</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="O20" t="inlineStr">
@@ -1622,9 +1634,11 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>必填字段为空: 中文表名, 业务定义; 域类型'i'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 必填字段为空: 中文表名, 业务定义
+2. 域类型'i'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="J21" t="inlineStr">
@@ -1670,9 +1684,11 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>域类型'INTEGER'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'INTEGER'格式不合法
+2. 字段中文名'手数'中'手'是催收行业术语（指催收轮次/次数），单独出现时含义不明，非见名知意的常见金融名称。业务含义与字段名完全相同，没有解释'手'的具体含义或业务背景，未提供实质信息，因此无效。</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="J22" t="inlineStr">
@@ -1717,6 +1733,7 @@
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="J23" t="inlineStr">
@@ -1762,9 +1779,10 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>域类型'DATE'不允许用于字段所属类型'编码类'</t>
-        </is>
-      </c>
+          <t>1. 域类型'DATE'不允许用于字段所属类型'编码类'</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="J24" t="inlineStr">
@@ -1810,9 +1828,10 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>域类型'VARCHAR(4)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'VARCHAR(4)'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="J25" t="inlineStr">
@@ -1858,9 +1877,10 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>域类型'INTEGER'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'INTEGER'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="J26" t="inlineStr">
@@ -1901,9 +1921,10 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>必填字段为空: 业务定义</t>
-        </is>
-      </c>
+          <t>1. 必填字段为空: 业务定义</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="J27" t="inlineStr">
@@ -1946,6 +1967,7 @@
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="J28" t="inlineStr">
@@ -1988,6 +2010,7 @@
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="J29" t="inlineStr">
@@ -2032,6 +2055,7 @@
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="J30" t="inlineStr">
@@ -2076,6 +2100,7 @@
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="J31" t="inlineStr">
@@ -2120,6 +2145,7 @@
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="J32" t="inlineStr">
@@ -2164,6 +2190,7 @@
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="J33" t="inlineStr">
@@ -2206,6 +2233,7 @@
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="J34" t="inlineStr">
@@ -2248,6 +2276,7 @@
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="J35" t="inlineStr">
@@ -2288,10 +2317,15 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>1. 标志类字段的'是否枚举'必须为'是'，实际为'否'</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="J36" t="inlineStr">
@@ -2332,10 +2366,15 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>1. 标志类字段的'是否枚举'必须为'是'，实际为'否'</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="J37" t="inlineStr">
@@ -2380,6 +2419,7 @@
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="J38" t="inlineStr">
@@ -2420,10 +2460,15 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'量子计算哈希值'不属于见名知意的常见金融业务名称，需要业务含义来解释。但业务含义'量子计算结果的哈希标识'与字段名在语义上基本等价，只是将'哈希值'换说成'哈希标识'，并添加'结果'二字，未提供任何实质性新信息，属于语义重复，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="J39" t="inlineStr">
@@ -2468,6 +2513,7 @@
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
     </row>
     <row r="40" ht="33" customHeight="1" s="26">
       <c r="J40" s="1" t="inlineStr">
@@ -2512,12 +2558,13 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an..(10)'不允许用于字段所属类型'标志类'</t>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>因为状态字段表示上传文档后该文档所处的状态，状态通常有多个取值（如已上传、处理中、已生效等），属于明确分类、多取值的数据项，应归为代码枚举类。而标志类仅适用于只有'是'和'否'两种取值的数据项，状态明显不止两种取值，因此填写为标志类不正确。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
         </is>
       </c>
     </row>
@@ -2564,6 +2611,7 @@
         </is>
       </c>
       <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
     </row>
     <row r="42" ht="33" customHeight="1" s="26">
       <c r="J42" s="1" t="inlineStr">
@@ -2608,6 +2656,11 @@
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>因为参数表编号是维护人员填写的编号，编号属于被赋予一定规律、便于计算机和人识别处理的符号，具有特定编码规则，应归为编码类，而非文本类。文本类适用于说明描述类信息，而编号是标识符号，因此填写为文本类不正确。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="33" customHeight="1" s="26">
       <c r="J43" s="1" t="inlineStr">
@@ -2652,6 +2705,7 @@
         </is>
       </c>
       <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
     </row>
     <row r="44" ht="33" customHeight="1" s="26">
       <c r="J44" s="1" t="inlineStr">
@@ -2696,6 +2750,7 @@
         </is>
       </c>
       <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
     </row>
     <row r="45" ht="33" customHeight="1" s="26">
       <c r="J45" s="1" t="inlineStr">
@@ -2741,9 +2796,10 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>域类型'an(11)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'an(11)'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr"/>
     </row>
     <row r="46" ht="33" customHeight="1" s="26">
       <c r="J46" s="1" t="inlineStr">
@@ -2789,9 +2845,10 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>域类型'an(7)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'an(7)'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr"/>
     </row>
     <row r="47" ht="33" customHeight="1" s="26">
       <c r="J47" s="1" t="inlineStr">
@@ -2836,6 +2893,7 @@
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
     </row>
     <row r="48" ht="33" customHeight="1" s="26">
       <c r="J48" s="1" t="inlineStr">
@@ -2880,6 +2938,7 @@
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
     </row>
     <row r="49" ht="33" customHeight="1" s="26">
       <c r="J49" s="1" t="inlineStr">
@@ -2924,12 +2983,13 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an..(10)'不允许用于字段所属类型'标志类'</t>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>因为状态字段用于表示模板维护后的状态，通常存在多种取值（如草稿、待审核、已发布、失效等），属于有明确分类的代码枚举类；而标志类仅适用于“是/否”两种取值的情况，因此填写为标志类可能错误，应为代码枚举类。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
         </is>
       </c>
     </row>
@@ -2976,6 +3036,7 @@
         </is>
       </c>
       <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
     </row>
     <row r="51" ht="33" customHeight="1" s="26">
       <c r="J51" s="1" t="inlineStr">
@@ -3020,6 +3081,7 @@
         </is>
       </c>
       <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
     </row>
     <row r="52" ht="33" customHeight="1" s="26">
       <c r="J52" s="1" t="inlineStr">
@@ -3064,6 +3126,11 @@
         </is>
       </c>
       <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>因为数据权限类型代码是表示数据权限类型的代码，属于具有特定编码规则、便于计算机和人识别处理的符号，应归为编码类；而文本类仅适用于说明描述类信息，故填写为文本类可能错误，应为编码类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="33" customHeight="1" s="26">
       <c r="J53" s="1" t="inlineStr">
@@ -3108,6 +3175,7 @@
         </is>
       </c>
       <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
     </row>
     <row r="54" ht="33" customHeight="1" s="26">
       <c r="J54" s="1" t="inlineStr">
@@ -3152,6 +3220,11 @@
         </is>
       </c>
       <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>因为数据权限代码KEY值1是数据权限代码中的键值（共5个属性之一），属于具有编码规则、用于标识和处理的符号，应归为编码类；虽然可能以文本形式存储，但其本质是代码值，填写为文本类可能错误，应为编码类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="33" customHeight="1" s="26">
       <c r="J55" s="1" t="inlineStr">
@@ -3196,6 +3269,11 @@
         </is>
       </c>
       <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>因为数据权限代码KEY值2是数据权限代码中的键值（共5个属性之一），属于具有编码规则、用于标识和处理的符号，应归为编码类；填写为文本类可能错误，应为编码类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="33" customHeight="1" s="26">
       <c r="J56" s="1" t="inlineStr">
@@ -3240,6 +3318,11 @@
         </is>
       </c>
       <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>因为字段名为'数据权限代码KEY值3'，业务定义为角色数据权限维护功能维护的数据权限代码KEY值，是数据权限代码中的KEY标识，属于具有特定编码规则的代码标识符，应属于编码类，而非说明描述类的文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="33" customHeight="1" s="26">
       <c r="J57" s="1" t="inlineStr">
@@ -3284,6 +3367,11 @@
         </is>
       </c>
       <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>因为字段名为'数据权限代码KEY值4'，是数据权限代码中的KEY标识，属于具有特定编码规则的代码值，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="33" customHeight="1" s="26">
       <c r="J58" s="1" t="inlineStr">
@@ -3328,6 +3416,11 @@
         </is>
       </c>
       <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>因为字段名为'数据权限代码KEY值5'，是数据权限代码中的KEY标识，属于具有特定编码规则的代码值，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="33" customHeight="1" s="26">
       <c r="J59" s="1" t="inlineStr">
@@ -3372,6 +3465,11 @@
         </is>
       </c>
       <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>因为字段名为'数据权限代码VALUE值1'，是数据权限代码中的VALUE值，作为代码配置的取值标识，具有特定编码规则，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="33" customHeight="1" s="26">
       <c r="J60" s="1" t="inlineStr">
@@ -3416,6 +3514,11 @@
         </is>
       </c>
       <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>因为字段名为'数据权限代码VALUE值2'，是数据权限代码中的VALUE值，属于具有特定编码规则的代码取值，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="33" customHeight="1" s="26">
       <c r="J61" s="1" t="inlineStr">
@@ -3460,6 +3563,11 @@
         </is>
       </c>
       <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>因为字段名为'数据权限代码VALUE值3'，是数据权限代码中的VALUE值，属于具有特定编码规则的代码取值，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="33" customHeight="1" s="26">
       <c r="J62" s="1" t="inlineStr">
@@ -3504,6 +3612,11 @@
         </is>
       </c>
       <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>因为字段名为'数据权限代码VALUE值4'，是数据权限代码中的VALUE值，属于具有特定编码规则的代码取值，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="33" customHeight="1" s="26">
       <c r="J63" s="1" t="inlineStr">
@@ -3548,6 +3661,11 @@
         </is>
       </c>
       <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>因为字段名为'数据权限代码VALUE值5'，是数据权限代码中的VALUE值，属于具有特定编码规则的代码取值，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="33" customHeight="1" s="26">
       <c r="J64" s="1" t="inlineStr">
@@ -3593,9 +3711,10 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>域类型'an(7)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'an(7)'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr"/>
     </row>
     <row r="65" ht="33" customHeight="1" s="26">
       <c r="J65" s="1" t="inlineStr">
@@ -3640,6 +3759,7 @@
         </is>
       </c>
       <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
     </row>
     <row r="66" ht="33" customHeight="1" s="26">
       <c r="J66" s="1" t="inlineStr">
@@ -3684,6 +3804,7 @@
         </is>
       </c>
       <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
     </row>
     <row r="67" ht="33" customHeight="1" s="26">
       <c r="J67" s="1" t="inlineStr">
@@ -3729,9 +3850,10 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>域类型'an(11)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'an(11)'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr"/>
     </row>
     <row r="68" ht="33" customHeight="1" s="26">
       <c r="J68" s="1" t="inlineStr">
@@ -3776,6 +3898,7 @@
         </is>
       </c>
       <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
     </row>
     <row r="69" ht="33" customHeight="1" s="26">
       <c r="J69" s="1" t="inlineStr">
@@ -3821,9 +3944,10 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>域类型'an(11)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'an(11)'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr"/>
     </row>
     <row r="70" ht="33" customHeight="1" s="26">
       <c r="J70" s="1" t="inlineStr">
@@ -3869,9 +3993,10 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>字段中文名'维护时间'在表'参数管理-角色数据权限信息表'中重复</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'维护时间'在表'参数管理-角色数据权限信息表'中重复</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr"/>
     </row>
     <row r="71" ht="33" customHeight="1" s="26">
       <c r="J71" s="1" t="inlineStr">
@@ -3917,9 +4042,10 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>字段中文名'维护时间'在表'参数管理-角色数据权限信息表'中重复</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'维护时间'在表'参数管理-角色数据权限信息表'中重复</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr"/>
     </row>
     <row r="72" ht="33" customHeight="1" s="26">
       <c r="J72" s="1" t="inlineStr">
@@ -3965,9 +4091,10 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>字段中文名'模板编号'表示模板的编号，而业务含义'关联参数模板维护功能维护这一条数据的时间'描述的是维护时间，两者语义完全不一致。业务含义描述的是'时间'属性，与字段名'模板编号'所指的编号属性相矛盾，未对字段进行正确解释，属于无效。</t>
-        </is>
-      </c>
+          <t>1. 字段中文名是'模板编号'，而业务含义描述的是'关联参数模板维护功能维护这一条数据的时间'，两者语义完全不对应——编号与时间是两种不同的属性，业务含义并未解释模板编号的含义，且与字段名不相关，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr"/>
     </row>
     <row r="73" ht="33" customHeight="1" s="26">
       <c r="J73" s="1" t="inlineStr">
@@ -4012,6 +4139,7 @@
         </is>
       </c>
       <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
     </row>
     <row r="74" ht="33" customHeight="1" s="26">
       <c r="J74" s="1" t="inlineStr">
@@ -4056,12 +4184,13 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an..(10)'不允许用于字段所属类型'标志类'</t>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>因为模板状态表示模板当前所处的状态（如生效、失效、草稿等），属于有明确分类、多取值的数据项，应归为代码枚举类；标志类仅适用于只有'是'和'否'两种取值的字段，与状态含义不符，因此填写为标志类可能错误。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
         </is>
       </c>
     </row>
@@ -4109,9 +4238,11 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>数据示例'一键多属性模板'不符合域类型'an..(30)'的限制: 包含汉字字符'一'（数字+字母+特殊符号类不允许汉字）; 字段中文名'模板类型'表示模板的类型，而业务含义'关联参数模板维护功能，维护关联参数以后，该模板的状态'描述的是模板的状态，两者语义不一致。业务含义描述的是'状态'属性，与字段名'模板类型'所指的类型属性相矛盾，未对字段进行正确解释，属于无效。</t>
-        </is>
-      </c>
+          <t>1. 数据示例'一键多属性模板'不符合域类型'an..(30)'的限制: 包含汉字字符'一'（数字+字母+特殊符号类不允许汉字）
+2. 字段中文名是'模板类型'，但业务含义'关联参数模板维护功能，维护关联参数以后，该模板的状态'描述的是'模板的状态'而非'模板的类型'，两者属性不同、语义错位，业务含义没有对'模板类型'做出解释，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr"/>
     </row>
     <row r="76" ht="33" customHeight="1" s="26">
       <c r="J76" s="1" t="inlineStr">
@@ -4157,9 +4288,10 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>字段中文名'参数模板归属团队'表示参数模板所属的团队，而业务含义'关联参数模板维护功能，维护人员通过功能输入的模板类型'描述的是模板类型，两者语义不一致。业务含义描述的是'模板类型'，与字段名'归属团队'所指的团队属性相矛盾，未对字段进行正确解释，属于无效。</t>
-        </is>
-      </c>
+          <t>1. 字段中文名是'参数模板归属团队'，表示模板所属的团队，而业务含义'关联参数模板维护功能，维护人员通过功能输入的模板类型'描述的是'模板类型'，与字段名表达的'归属团队'完全不匹配，两者没有语义联系，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr"/>
     </row>
     <row r="77" ht="33" customHeight="1" s="26">
       <c r="J77" s="1" t="inlineStr">
@@ -4204,6 +4336,11 @@
         </is>
       </c>
       <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>因为参数模板维护团队是维护人员通过功能从已有团队选项中选取的归属团队，属于有明确分类或固定取值集合的数据项，应归为代码枚举类；编码类要求数据具有特定编码规则（如证件号码、机构代码），而此处是通过功能选择团队而非按编码规则生成，因此填写为编码类可能错误。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="33" customHeight="1" s="26">
       <c r="J78" s="1" t="inlineStr">
@@ -4244,10 +4381,15 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'创建人'指的是创建该模板的人员，而业务含义'关联参数模板维护功能，维护人员通过功能选择的参数模板维护团队'描述的是维护团队，与'创建人'所指的人员概念不一致，业务含义与字段名所表达的内容不相关，未对'创建人'作任何解释，无效。</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr"/>
     </row>
     <row r="79" ht="33" customHeight="1" s="26">
       <c r="J79" s="1" t="inlineStr">
@@ -4288,10 +4430,15 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'创建时间'指模板创建的时间，而业务含义'关联参数模板维护功能，创建该模板的人员的用户号'描述的是创建人员的用户号，属于人员信息而非时间信息，与字段名'创建时间'不相关，未对创建时间作任何说明，无效。</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr"/>
     </row>
     <row r="80" ht="33" customHeight="1" s="26">
       <c r="J80" s="1" t="inlineStr">
@@ -4332,10 +4479,15 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'最后操作人'指最后操作该模板的人员，而业务含义'关联参数模板维护功能，创建该模板时的时间'描述的是模板创建时间，属于时间信息而非操作人员信息，与字段名'最后操作人'不相关，无效。</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr"/>
     </row>
     <row r="81" ht="33" customHeight="1" s="26">
       <c r="J81" s="1" t="inlineStr">
@@ -4380,6 +4532,7 @@
         </is>
       </c>
       <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
     </row>
     <row r="82" ht="33" customHeight="1" s="26">
       <c r="J82" s="1" t="inlineStr">
@@ -4420,10 +4573,15 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'模板编号'指模板的编号标识，而业务含义'关联参数模板维护功能，创建该模板后，该模板最后被维护的时间'描述的是模板最后被维护的时间，属于时间信息而非编号信息，与字段名'模板编号'不相关，无效。</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr"/>
     </row>
     <row r="83" ht="33" customHeight="1" s="26">
       <c r="J83" s="1" t="inlineStr">
@@ -4469,9 +4627,11 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>数据示例'是否二级分类'不符合域类型'an..(50)'的限制: 包含汉字字符'是'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'是否二级分类'不符合域类型'an..(50)'的限制: 包含汉字字符'是'（数字+字母+特殊符号类不允许汉字）
+2. 字段中文名'模板属性'指模板的属性信息，而业务含义'关联参数模板维护功能，维护人员通过功能输入的模板编号'描述的是维护人员输入的模板编号，属于编号信息而非模板属性，与字段名'模板属性'不相关，无效。</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr"/>
     </row>
     <row r="84" ht="33" customHeight="1" s="26">
       <c r="J84" s="1" t="inlineStr">
@@ -4512,10 +4672,15 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'属性编码'指属性的编码值，而业务含义'关联参数模板维护功能，维护人员通过功能输入的模板属性'描述的是模板属性而非属性编码，与字段名'属性编码'所表达的概念不一致，不相关，无效。</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr"/>
     </row>
     <row r="85" ht="33" customHeight="1" s="26">
       <c r="J85" s="1" t="inlineStr">
@@ -4556,10 +4721,15 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'属性顺序'指属性排列的顺序，而业务含义'关联参数模板维护功能，维护人员通过功能输入的属性编码'描述的是属性编码而非属性顺序，与字段名'属性顺序'不相关，未对顺序作任何说明，无效。</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr"/>
     </row>
     <row r="86" ht="33" customHeight="1" s="26">
       <c r="J86" s="1" t="inlineStr">
@@ -4604,12 +4774,13 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an..(20)'不允许用于字段所属类型'标志类'</t>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>因为属性类型表示属性的种类，是维护人员通过功能从预定义类型选项中选取的，属于有明确分类、多取值的数据项，应归为代码枚举类；标志类仅适用于只有'是'和'否'两种取值的字段，与类型含义不符，因此填写为标志类可能错误。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4827,13 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an..(20)'不允许用于字段所属类型'标志类'</t>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>因为属性状态表示属性维护后所处的状态（如正常、停用等），属于有明确分类、多取值的数据项，应归为代码枚举类；标志类仅适用于只有'是'和'否'两种取值的字段，状态字段通常不止两种取值，因此填写为标志类可能错误。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
         </is>
       </c>
     </row>
@@ -4708,6 +4880,7 @@
         </is>
       </c>
       <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="inlineStr"/>
     </row>
     <row r="89" ht="33" customHeight="1" s="26">
       <c r="J89" s="1" t="inlineStr">
@@ -4752,6 +4925,7 @@
         </is>
       </c>
       <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="inlineStr"/>
     </row>
     <row r="90" ht="33" customHeight="1" s="26">
       <c r="J90" s="1" t="inlineStr">
@@ -4796,6 +4970,7 @@
         </is>
       </c>
       <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="inlineStr"/>
     </row>
     <row r="91" ht="33" customHeight="1" s="26">
       <c r="J91" s="1" t="inlineStr">
@@ -4840,6 +5015,7 @@
         </is>
       </c>
       <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="inlineStr"/>
     </row>
     <row r="92" ht="33" customHeight="1" s="26">
       <c r="J92" s="1" t="inlineStr">
@@ -4884,14 +5060,11 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an..(2)'不允许用于字段所属类型'标志类'</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="inlineStr"/>
     </row>
     <row r="93" ht="33" customHeight="1" s="26">
       <c r="J93" s="1" t="inlineStr">
@@ -4936,14 +5109,11 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an..(2)'不允许用于字段所属类型'标志类'</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr"/>
+      <c r="AC93" t="inlineStr"/>
     </row>
     <row r="94" ht="33" customHeight="1" s="26">
       <c r="J94" s="1" t="inlineStr">
@@ -4988,14 +5158,11 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an..(2)'不允许用于字段所属类型'标志类'</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr"/>
     </row>
     <row r="95" ht="33" customHeight="1" s="26">
       <c r="J95" s="1" t="inlineStr">
@@ -5040,6 +5207,11 @@
         </is>
       </c>
       <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>因为字段名为“属性与属性关系”，业务定义为维护人员选择的属性与属性关系，说明该字段是从预定义的关系类型（如父子、同级等）中选择的取值，属于有明确分类的枚举信息，应属于代码枚举类，而非自由填写的文本类。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="33" customHeight="1" s="26">
       <c r="J96" s="1" t="inlineStr">
@@ -5084,6 +5256,7 @@
         </is>
       </c>
       <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="inlineStr"/>
     </row>
     <row r="97" ht="33" customHeight="1" s="26">
       <c r="J97" s="1" t="inlineStr">
@@ -5128,6 +5301,7 @@
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="inlineStr"/>
     </row>
     <row r="98" ht="33" customHeight="1" s="26">
       <c r="J98" s="1" t="inlineStr">
@@ -5173,9 +5347,10 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>数据示例'是否二级分类'不符合域类型'an..(50)'的限制: 包含汉字字符'是'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'是否二级分类'不符合域类型'an..(50)'的限制: 包含汉字字符'是'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr"/>
     </row>
     <row r="99" ht="33" customHeight="1" s="26">
       <c r="J99" s="1" t="inlineStr">
@@ -5220,6 +5395,7 @@
         </is>
       </c>
       <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr"/>
     </row>
     <row r="100" ht="33" customHeight="1" s="26">
       <c r="J100" s="1" t="inlineStr">
@@ -5264,12 +5440,13 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an..(20)'不允许用于字段所属类型'标志类'</t>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>因为字段名为“属性状态”，业务定义为该属性值的状态，状态通常包含多种取值（如启用、停用、待审核等），而非仅“是/否”两种取值的标志类，应属于代码枚举类。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
         </is>
       </c>
     </row>
@@ -5316,6 +5493,11 @@
         </is>
       </c>
       <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>因为字段名为“属性编码”，业务定义为维护人员输入的属性编码，编码是具有特定编码规则、便于计算机和人识别处理的符号，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="33" customHeight="1" s="26">
       <c r="J102" s="1" t="inlineStr">
@@ -5360,12 +5542,13 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'an..(20)'不允许用于字段所属类型'标志类'</t>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>因为属性类型表示属性的一种分类取值，维护人员通过功能可选择不同的属性类型，说明该字段有多种明确的分类/取值，应属于代码枚举类。而标志类仅适用于只有'是'和'否'两种取值的数据项，与'属性类型'可多值取样的语义不符，因此填写为标志类可能错误。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
         </is>
       </c>
     </row>
@@ -5410,6 +5593,7 @@
         </is>
       </c>
       <c r="AB103" t="inlineStr"/>
+      <c r="AC103" t="inlineStr"/>
     </row>
     <row r="104" ht="16.5" customHeight="1" s="26">
       <c r="J104" s="2" t="inlineStr">
@@ -5452,6 +5636,7 @@
         </is>
       </c>
       <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="inlineStr"/>
     </row>
     <row r="105" ht="16.5" customHeight="1" s="26">
       <c r="J105" s="2" t="inlineStr">
@@ -5494,6 +5679,7 @@
         </is>
       </c>
       <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="inlineStr"/>
     </row>
     <row r="106" ht="27" customHeight="1" s="26">
       <c r="J106" s="2" t="inlineStr">
@@ -5540,6 +5726,7 @@
         </is>
       </c>
       <c r="AB106" t="inlineStr"/>
+      <c r="AC106" t="inlineStr"/>
     </row>
     <row r="107" ht="16.5" customHeight="1" s="26">
       <c r="J107" s="2" t="inlineStr">
@@ -5582,6 +5769,7 @@
         </is>
       </c>
       <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="inlineStr"/>
     </row>
     <row r="108" ht="16.5" customHeight="1" s="26">
       <c r="J108" s="2" t="inlineStr">
@@ -5625,9 +5813,10 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>数据示例'2029-01-01 00:00:00'不符合域类型'DATE'的限制: DATE应为8位日期数字（YYYYMMDD），实际14位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2029-01-01 00:00:00'不符合域类型'DATE'的限制: DATE应为8位日期数字（YYYYMMDD），实际14位</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr"/>
     </row>
     <row r="109" ht="33" customHeight="1" s="26">
       <c r="J109" s="2" t="inlineStr">
@@ -5670,6 +5859,7 @@
         </is>
       </c>
       <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="inlineStr"/>
     </row>
     <row r="110" ht="33" customHeight="1" s="26">
       <c r="J110" s="2" t="inlineStr">
@@ -5712,6 +5902,7 @@
         </is>
       </c>
       <c r="AB110" t="inlineStr"/>
+      <c r="AC110" t="inlineStr"/>
     </row>
     <row r="111" ht="16.5" customHeight="1" s="26">
       <c r="J111" s="2" t="inlineStr">
@@ -5754,6 +5945,7 @@
         </is>
       </c>
       <c r="AB111" t="inlineStr"/>
+      <c r="AC111" t="inlineStr"/>
     </row>
     <row r="112" ht="33" customHeight="1" s="26">
       <c r="J112" s="2" t="inlineStr">
@@ -5797,9 +5989,10 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>数据示例'2029-01-01 00:00:00'不符合域类型'DATE'的限制: DATE应为8位日期数字（YYYYMMDD），实际14位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2029-01-01 00:00:00'不符合域类型'DATE'的限制: DATE应为8位日期数字（YYYYMMDD），实际14位</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr"/>
     </row>
     <row r="113" ht="33" customHeight="1" s="26">
       <c r="J113" s="2" t="inlineStr">
@@ -5842,6 +6035,7 @@
         </is>
       </c>
       <c r="AB113" t="inlineStr"/>
+      <c r="AC113" t="inlineStr"/>
     </row>
     <row r="114" ht="33" customHeight="1" s="26">
       <c r="J114" s="2" t="inlineStr">
@@ -5884,6 +6078,7 @@
         </is>
       </c>
       <c r="AB114" t="inlineStr"/>
+      <c r="AC114" t="inlineStr"/>
     </row>
     <row r="115" ht="33" customHeight="1" s="26">
       <c r="J115" s="2" t="inlineStr">
@@ -5927,9 +6122,10 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>数据示例'0.0055'不符合域类型'i(5,1)'的限制: 小数部分不得超过1位，实际4位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'0.0055'不符合域类型'i(5,1)'的限制: 小数部分不得超过1位，实际4位</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr"/>
     </row>
     <row r="116" ht="66" customHeight="1" s="26">
       <c r="J116" s="2" t="inlineStr">
@@ -5972,6 +6168,7 @@
         </is>
       </c>
       <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="inlineStr"/>
     </row>
     <row r="117" ht="33" customHeight="1" s="26">
       <c r="J117" s="2" t="inlineStr">
@@ -6014,6 +6211,7 @@
         </is>
       </c>
       <c r="AB117" t="inlineStr"/>
+      <c r="AC117" t="inlineStr"/>
     </row>
     <row r="118" ht="33" customHeight="1" s="26">
       <c r="J118" s="2" t="inlineStr">
@@ -6057,9 +6255,10 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>数据示例'0.0305'不符合域类型'i(5,1)'的限制: 小数部分不得超过1位，实际4位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'0.0305'不符合域类型'i(5,1)'的限制: 小数部分不得超过1位，实际4位</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr"/>
     </row>
     <row r="119" ht="16.5" customHeight="1" s="26">
       <c r="J119" s="2" t="inlineStr">
@@ -6102,6 +6301,7 @@
         </is>
       </c>
       <c r="AB119" t="inlineStr"/>
+      <c r="AC119" t="inlineStr"/>
     </row>
     <row r="120" ht="16.5" customHeight="1" s="26">
       <c r="J120" s="2" t="inlineStr">
@@ -6144,6 +6344,7 @@
         </is>
       </c>
       <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="inlineStr"/>
     </row>
     <row r="121" ht="16.5" customHeight="1" s="26">
       <c r="J121" s="2" t="inlineStr">
@@ -6187,9 +6388,10 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>字段中文名'总Token数'与业务含义'总的Token数'在语义上完全等价，业务含义只是在原名称基础上添加了无实质意义的'的'字，未提供任何额外信息，属于简单加词，判定为无效。</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'总Token数'与业务含义'总的Token数'语义完全相同，业务含义只是在原名称基础上添加无实质意义的'的'字，未提供任何新信息，属于简单加词，无效。</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr"/>
     </row>
     <row r="122" ht="16.5" customHeight="1" s="26">
       <c r="J122" s="2" t="inlineStr">
@@ -6239,9 +6441,10 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>字段中文名'影子模型标志'与业务含义'影子模型判断标志'语义基本等价，业务含义只是在原名称基础上添加了'判断'二字，'标志'本身已隐含判断的含义，未提供实质性的额外信息，属于简单加词，判定为无效。</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'影子模型标志'本身已表达'影子模型的标识'之意，业务含义'影子模型判断标志'只是在原名称基础上添加'判断'二字，两者语义基本等价，未提供实质性的新信息，属于简单加词/语义重复，无效。</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr"/>
     </row>
     <row r="123" ht="27" customHeight="1" s="26">
       <c r="J123" s="2" t="inlineStr">
@@ -6286,6 +6489,7 @@
         </is>
       </c>
       <c r="AB123" t="inlineStr"/>
+      <c r="AC123" t="inlineStr"/>
     </row>
     <row r="124" ht="33" customHeight="1" s="26">
       <c r="J124" s="2" t="inlineStr">
@@ -6330,6 +6534,7 @@
         </is>
       </c>
       <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr"/>
     </row>
     <row r="125" ht="16.5" customHeight="1" s="26">
       <c r="J125" s="2" t="inlineStr">
@@ -6379,9 +6584,11 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>代码枚举类字段的'是否枚举'必须为'是'，实际为'否'; '是否枚举'为'否'但枚举值不为空</t>
-        </is>
-      </c>
+          <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
+2. '是否枚举'为'否'但枚举值不为空</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr"/>
     </row>
     <row r="126" ht="16.5" customHeight="1" s="26">
       <c r="J126" s="2" t="inlineStr">
@@ -6424,6 +6631,7 @@
         </is>
       </c>
       <c r="AB126" t="inlineStr"/>
+      <c r="AC126" t="inlineStr"/>
     </row>
     <row r="127" ht="16.5" customHeight="1" s="26">
       <c r="J127" s="2" t="inlineStr">
@@ -6466,6 +6674,7 @@
         </is>
       </c>
       <c r="AB127" t="inlineStr"/>
+      <c r="AC127" t="inlineStr"/>
     </row>
     <row r="128" ht="33" customHeight="1" s="26">
       <c r="J128" s="2" t="inlineStr">
@@ -6515,9 +6724,10 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>1. 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr"/>
     </row>
     <row r="129" ht="33" customHeight="1" s="26">
       <c r="J129" s="2" t="inlineStr">
@@ -6562,6 +6772,7 @@
         </is>
       </c>
       <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="inlineStr"/>
     </row>
     <row r="130" ht="115.5" customHeight="1" s="26">
       <c r="J130" s="8" t="inlineStr">
@@ -6606,10 +6817,15 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'处理状态'与业务含义'指系统的处理状态'在语义上基本等价，只是在原名称基础上添加了'指'和'系统的'等词语，并未说明具体是何种处理、哪个系统的处理等实质信息，属于简单加词/语义重复，未提供字段名之外的新信息，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr"/>
     </row>
     <row r="131" ht="16.5" customHeight="1" s="26">
       <c r="J131" s="8" t="inlineStr">
@@ -6655,9 +6871,10 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr"/>
     </row>
     <row r="132" ht="16.5" customHeight="1" s="26">
       <c r="J132" s="8" t="inlineStr">
@@ -6703,9 +6920,10 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr"/>
     </row>
     <row r="133" ht="16.5" customHeight="1" s="26">
       <c r="J133" s="8" t="inlineStr">
@@ -6751,9 +6969,10 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr"/>
     </row>
     <row r="134" ht="16.5" customHeight="1" s="26">
       <c r="J134" s="8" t="inlineStr">
@@ -6799,9 +7018,10 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr"/>
     </row>
     <row r="135" ht="33" customHeight="1" s="26">
       <c r="J135" s="8" t="inlineStr">
@@ -6847,9 +7067,10 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr"/>
     </row>
     <row r="136" ht="33" customHeight="1" s="26">
       <c r="J136" s="8" t="inlineStr">
@@ -6895,9 +7116,10 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr"/>
     </row>
     <row r="137" ht="247.5" customHeight="1" s="26">
       <c r="J137" s="8" t="inlineStr">
@@ -6946,6 +7168,7 @@
         </is>
       </c>
       <c r="AB137" t="inlineStr"/>
+      <c r="AC137" t="inlineStr"/>
     </row>
     <row r="138" ht="16.5" customHeight="1" s="26">
       <c r="J138" s="8" t="inlineStr">
@@ -6991,9 +7214,10 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr"/>
     </row>
     <row r="139" ht="16.5" customHeight="1" s="26">
       <c r="J139" s="8" t="inlineStr">
@@ -7039,9 +7263,10 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr"/>
     </row>
     <row r="140" ht="33" customHeight="1" s="26">
       <c r="J140" s="8" t="inlineStr">
@@ -7087,9 +7312,10 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr"/>
     </row>
     <row r="141" ht="49.5" customHeight="1" s="26">
       <c r="J141" s="8" t="inlineStr">
@@ -7124,7 +7350,9 @@
       </c>
       <c r="W141" s="9" t="inlineStr">
         <is>
-          <t>01-新增合作;02-维持合作;03-停止合作</t>
+          <t>新增合作
+维持合作
+停止合作</t>
         </is>
       </c>
       <c r="Y141" s="9" t="inlineStr">
@@ -7134,10 +7362,15 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>1. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr"/>
     </row>
     <row r="142" ht="132" customHeight="1" s="26">
       <c r="J142" s="8" t="inlineStr">
@@ -7187,6 +7420,7 @@
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr"/>
     </row>
     <row r="143" ht="16.5" customHeight="1" s="26">
       <c r="J143" s="8" t="inlineStr">
@@ -7232,9 +7466,10 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr"/>
     </row>
     <row r="144" ht="115.5" customHeight="1" s="26">
       <c r="J144" s="8" t="inlineStr">
@@ -7279,14 +7514,11 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>字段中文名'预约状态'业务含义'指报表预约的预约状态'只是在原名称基础上添加了'报表'一词，核心语义仍是'预约状态'，与字段中文名语义等价，属于简单加词/语义重复，未提供实质性的新信息，判定为无效。</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr"/>
     </row>
     <row r="145" ht="16.5" customHeight="1" s="26">
       <c r="J145" s="8" t="inlineStr">
@@ -7331,6 +7563,7 @@
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr"/>
     </row>
     <row r="146" ht="16.5" customHeight="1" s="26">
       <c r="J146" s="8" t="inlineStr">
@@ -7376,9 +7609,10 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr"/>
     </row>
     <row r="147" ht="33" customHeight="1" s="26">
       <c r="J147" s="8" t="inlineStr">
@@ -7428,9 +7662,10 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>字段中文名'产品类型'在表'无'中重复</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'产品类型'在表'无'中重复</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr"/>
     </row>
     <row r="148" ht="16.5" customHeight="1" s="26">
       <c r="J148" s="8" t="inlineStr">
@@ -7465,7 +7700,7 @@
       </c>
       <c r="W148" s="9" t="inlineStr">
         <is>
-          <t>01-/</t>
+          <t>/</t>
         </is>
       </c>
       <c r="Y148" s="9" t="inlineStr">
@@ -7480,9 +7715,11 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>'是否枚举'为'否'但枚举值不为空</t>
-        </is>
-      </c>
+          <t>1. '是否枚举'为'否'但枚举值不为空
+2. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr"/>
     </row>
     <row r="149" ht="33" customHeight="1" s="26">
       <c r="J149" s="8" t="inlineStr">
@@ -7528,9 +7765,10 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>数据示例'没给'不符合域类型'date'的限制: 包含非法字符'没'（日期时间类仅允许数字和分隔符-:/空格/T）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'没给'不符合域类型'date'的限制: 包含非法字符'没'（日期时间类仅允许数字和分隔符-:/空格/T）</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr"/>
     </row>
     <row r="150" ht="16.5" customHeight="1" s="26">
       <c r="J150" s="8" t="inlineStr">
@@ -7574,9 +7812,10 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>域类型'i'格式不合法; 字段中文名'成立日单位净值'本身含义清晰（成立日的单位净值），业务含义'产品成立日的单位净值'只是在原名称基础上添加'产品'和'的'，语义上完全等价，未提供任何新信息，属于语义重复，无效。</t>
-        </is>
-      </c>
+          <t>1. 域类型'i'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr"/>
     </row>
     <row r="151" ht="16.5" customHeight="1" s="26">
       <c r="J151" s="8" t="inlineStr">
@@ -7622,9 +7861,10 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>域类型'i'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'i'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr"/>
     </row>
     <row r="152" ht="33" customHeight="1" s="26">
       <c r="J152" s="8" t="inlineStr">
@@ -7669,6 +7909,7 @@
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr"/>
     </row>
     <row r="153" ht="33" customHeight="1" s="26">
       <c r="J153" s="8" t="inlineStr">
@@ -7713,14 +7954,11 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>字段中文名'理财产品收益类型'本身含义清晰，业务含义'用于标志理财产品的收益类型'只是在原名称基础上添加'用于标志'和'的'，语义上完全等价，未提供任何新信息，属于语义重复，无效。</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr"/>
     </row>
     <row r="154" ht="33" customHeight="1" s="26">
       <c r="J154" s="8" t="inlineStr">
@@ -7765,6 +8003,11 @@
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>因为父资产类型指的是理财产品投资的资产类型，如股票、基金、债券等，这些是有明确分类、多取值的类型数据，应属于代码枚举类而非文本类。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="33" customHeight="1" s="26">
       <c r="J155" s="8" t="inlineStr">
@@ -7813,6 +8056,7 @@
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
+      <c r="AC155" t="inlineStr"/>
     </row>
     <row r="156" ht="16.5" customHeight="1" s="26">
       <c r="J156" s="8" t="inlineStr">
@@ -7857,6 +8101,7 @@
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr"/>
     </row>
     <row r="157" ht="16.5" customHeight="1" s="26">
       <c r="J157" s="8" t="inlineStr">
@@ -7901,6 +8146,7 @@
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr"/>
     </row>
     <row r="158" ht="33" customFormat="1" customHeight="1" s="10">
       <c r="J158" s="22" t="inlineStr">
@@ -7945,10 +8191,15 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>1. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr"/>
     </row>
     <row r="159" ht="49.5" customHeight="1" s="26">
       <c r="J159" s="8" t="inlineStr">
@@ -7997,6 +8248,7 @@
         </is>
       </c>
       <c r="AB159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr"/>
     </row>
     <row r="160" ht="16.5" customHeight="1" s="26">
       <c r="J160" s="8" t="inlineStr">
@@ -8040,9 +8292,10 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>数据示例'1.5283'不符合域类型'i(5,1)'的限制: 小数部分不得超过1位，实际4位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'1.5283'不符合域类型'i(5,1)'的限制: 小数部分不得超过1位，实际4位</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr"/>
     </row>
     <row r="161" ht="33" customHeight="1" s="26">
       <c r="J161" s="8" t="inlineStr">
@@ -8086,9 +8339,10 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>数据示例'1.5283'不符合域类型'i(5,1)'的限制: 小数部分不得超过1位，实际4位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'1.5283'不符合域类型'i(5,1)'的限制: 小数部分不得超过1位，实际4位</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr"/>
     </row>
     <row r="162" ht="66" customHeight="1" s="26">
       <c r="J162" s="8" t="inlineStr">
@@ -8138,9 +8392,10 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>字段中文名'产品类型'在表'无'中重复</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'产品类型'在表'无'中重复</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr"/>
     </row>
     <row r="163" ht="16.5" customHeight="1" s="26">
       <c r="J163" s="8" t="inlineStr">
@@ -8190,9 +8445,11 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>'是否枚举'为'否'但枚举值不为空</t>
-        </is>
-      </c>
+          <t>1. '是否枚举'为'否'但枚举值不为空
+2. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr"/>
     </row>
     <row r="164" ht="16.5" customHeight="1" s="26">
       <c r="J164" s="8" t="inlineStr">
@@ -8237,6 +8494,7 @@
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr"/>
     </row>
     <row r="165" ht="33" customHeight="1" s="26">
       <c r="J165" s="8" t="inlineStr">
@@ -8281,6 +8539,7 @@
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
     </row>
     <row r="166" ht="33" customHeight="1" s="26">
       <c r="J166" s="8" t="inlineStr">
@@ -8325,6 +8584,7 @@
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
     </row>
     <row r="167" ht="16.5" customHeight="1" s="26">
       <c r="J167" s="8" t="inlineStr">
@@ -8369,6 +8629,7 @@
         </is>
       </c>
       <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="inlineStr"/>
     </row>
     <row r="168" ht="33" customHeight="1" s="26">
       <c r="J168" s="8" t="inlineStr">
@@ -8412,9 +8673,10 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>数据示例'0.0522'不符合域类型'i(4,2)'的限制: 小数部分不得超过2位，实际4位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'0.0522'不符合域类型'i(4,2)'的限制: 小数部分不得超过2位，实际4位</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr"/>
     </row>
     <row r="169" ht="33" customHeight="1" s="26">
       <c r="J169" s="8" t="inlineStr">
@@ -8459,6 +8721,7 @@
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr"/>
     </row>
     <row r="170" ht="33" customHeight="1" s="26">
       <c r="J170" s="8" t="inlineStr">
@@ -8503,6 +8766,7 @@
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr"/>
     </row>
     <row r="171" ht="33" customHeight="1" s="26">
       <c r="J171" s="8" t="inlineStr">
@@ -8547,6 +8811,7 @@
         </is>
       </c>
       <c r="AB171" t="inlineStr"/>
+      <c r="AC171" t="inlineStr"/>
     </row>
     <row r="172" ht="33" customHeight="1" s="26">
       <c r="J172" s="8" t="inlineStr">
@@ -8591,6 +8856,7 @@
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
+      <c r="AC172" t="inlineStr"/>
     </row>
     <row r="173" ht="33" customHeight="1" s="26">
       <c r="J173" s="8" t="inlineStr">
@@ -8635,6 +8901,7 @@
         </is>
       </c>
       <c r="AB173" t="inlineStr"/>
+      <c r="AC173" t="inlineStr"/>
     </row>
     <row r="174" ht="16.5" customHeight="1" s="26">
       <c r="J174" s="8" t="inlineStr">
@@ -8679,6 +8946,7 @@
         </is>
       </c>
       <c r="AB174" t="inlineStr"/>
+      <c r="AC174" t="inlineStr"/>
     </row>
     <row r="175" ht="16.5" customHeight="1" s="26">
       <c r="J175" s="8" t="inlineStr">
@@ -8713,7 +8981,7 @@
       </c>
       <c r="W175" s="9" t="inlineStr">
         <is>
-          <t>01-流入;02-流出</t>
+          <t>流入，流出</t>
         </is>
       </c>
       <c r="Y175" s="9" t="inlineStr">
@@ -8723,10 +8991,15 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>1. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr"/>
     </row>
     <row r="176" ht="16.5" customHeight="1" s="26">
       <c r="J176" s="8" t="inlineStr">
@@ -8771,6 +9044,7 @@
         </is>
       </c>
       <c r="AB176" t="inlineStr"/>
+      <c r="AC176" t="inlineStr"/>
     </row>
     <row r="177" ht="16.5" customHeight="1" s="26">
       <c r="J177" s="8" t="inlineStr">
@@ -8815,6 +9089,7 @@
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
+      <c r="AC177" t="inlineStr"/>
     </row>
     <row r="178" ht="16.5" customHeight="1" s="26">
       <c r="J178" s="8" t="inlineStr">
@@ -8849,7 +9124,7 @@
       </c>
       <c r="W178" s="9" t="inlineStr">
         <is>
-          <t>01-收款;02-付款</t>
+          <t>收款，付款</t>
         </is>
       </c>
       <c r="Y178" s="9" t="inlineStr">
@@ -8859,10 +9134,15 @@
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>1. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr"/>
     </row>
     <row r="179" ht="16.5" customHeight="1" s="26">
       <c r="J179" s="8" t="inlineStr">
@@ -8907,6 +9187,7 @@
         </is>
       </c>
       <c r="AB179" t="inlineStr"/>
+      <c r="AC179" t="inlineStr"/>
     </row>
     <row r="180" ht="16.5" customHeight="1" s="26">
       <c r="J180" s="8" t="inlineStr">
@@ -8952,9 +9233,10 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>域类型'anc'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'anc'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr"/>
     </row>
     <row r="181" ht="49.5" customHeight="1" s="26">
       <c r="J181" s="8" t="inlineStr">
@@ -8999,6 +9281,7 @@
         </is>
       </c>
       <c r="AB181" t="inlineStr"/>
+      <c r="AC181" t="inlineStr"/>
     </row>
     <row r="182" ht="49.5" customHeight="1" s="26">
       <c r="J182" s="8" t="inlineStr">
@@ -9043,6 +9326,7 @@
         </is>
       </c>
       <c r="AB182" t="inlineStr"/>
+      <c r="AC182" t="inlineStr"/>
     </row>
     <row r="183" ht="49.5" customHeight="1" s="26">
       <c r="J183" s="8" t="inlineStr">
@@ -9087,6 +9371,7 @@
         </is>
       </c>
       <c r="AB183" t="inlineStr"/>
+      <c r="AC183" t="inlineStr"/>
     </row>
     <row r="184" ht="49.5" customHeight="1" s="26">
       <c r="J184" s="8" t="inlineStr">
@@ -9131,6 +9416,7 @@
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
+      <c r="AC184" t="inlineStr"/>
     </row>
     <row r="185" ht="49.5" customHeight="1" s="26">
       <c r="J185" s="8" t="inlineStr">
@@ -9175,6 +9461,7 @@
         </is>
       </c>
       <c r="AB185" t="inlineStr"/>
+      <c r="AC185" t="inlineStr"/>
     </row>
     <row r="186" ht="66" customHeight="1" s="26">
       <c r="J186" s="8" t="inlineStr">
@@ -9219,6 +9506,7 @@
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
+      <c r="AC186" t="inlineStr"/>
     </row>
     <row r="187" ht="49.5" customHeight="1" s="26">
       <c r="J187" s="8" t="inlineStr">
@@ -9263,6 +9551,7 @@
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
+      <c r="AC187" t="inlineStr"/>
     </row>
     <row r="188" ht="49.5" customHeight="1" s="26">
       <c r="J188" s="8" t="inlineStr">
@@ -9307,6 +9596,7 @@
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
+      <c r="AC188" t="inlineStr"/>
     </row>
     <row r="189" ht="49.5" customHeight="1" s="26">
       <c r="J189" s="8" t="inlineStr">
@@ -9351,6 +9641,7 @@
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
+      <c r="AC189" t="inlineStr"/>
     </row>
     <row r="190" ht="66" customHeight="1" s="26">
       <c r="J190" s="8" t="inlineStr">
@@ -9395,6 +9686,7 @@
         </is>
       </c>
       <c r="AB190" t="inlineStr"/>
+      <c r="AC190" t="inlineStr"/>
     </row>
     <row r="191" ht="49.5" customHeight="1" s="26">
       <c r="J191" s="8" t="inlineStr">
@@ -9439,6 +9731,7 @@
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
+      <c r="AC191" t="inlineStr"/>
     </row>
     <row r="192" ht="49.5" customHeight="1" s="26">
       <c r="J192" s="8" t="inlineStr">
@@ -9483,6 +9776,7 @@
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
+      <c r="AC192" t="inlineStr"/>
     </row>
     <row r="193" ht="49.5" customHeight="1" s="26">
       <c r="J193" s="8" t="inlineStr">
@@ -9527,6 +9821,7 @@
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
+      <c r="AC193" t="inlineStr"/>
     </row>
     <row r="194" ht="66" customHeight="1" s="26">
       <c r="J194" s="8" t="inlineStr">
@@ -9571,6 +9866,7 @@
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
+      <c r="AC194" t="inlineStr"/>
     </row>
     <row r="195" ht="49.5" customHeight="1" s="26">
       <c r="J195" s="8" t="inlineStr">
@@ -9615,6 +9911,7 @@
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
+      <c r="AC195" t="inlineStr"/>
     </row>
     <row r="196" ht="16.5" customHeight="1" s="26">
       <c r="J196" s="8" t="inlineStr">
@@ -9649,7 +9946,7 @@
       </c>
       <c r="W196" s="9" t="inlineStr">
         <is>
-          <t>01-付款指令;02-收款指令</t>
+          <t>付款指令、收款指令</t>
         </is>
       </c>
       <c r="Y196" s="9" t="inlineStr">
@@ -9659,10 +9956,15 @@
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>1. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr"/>
     </row>
     <row r="197" ht="33" customHeight="1" s="26">
       <c r="J197" s="8" t="inlineStr">
@@ -9711,6 +10013,7 @@
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
+      <c r="AC197" t="inlineStr"/>
     </row>
     <row r="198" ht="33" customHeight="1" s="26">
       <c r="J198" s="8" t="inlineStr">
@@ -9756,9 +10059,10 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>域类型'i'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'i'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr"/>
     </row>
     <row r="199" ht="33" customHeight="1" s="26">
       <c r="J199" s="8" t="inlineStr">
@@ -9804,9 +10108,11 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; '是否枚举'为'是'但枚举值为空</t>
-        </is>
-      </c>
+          <t>1. 非代码枚举类/标志类字段的'是否枚举'必须为'否'，实际为'是'
+2. '是否枚举'为'是'但枚举值为空</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr"/>
     </row>
     <row r="200" ht="33" customHeight="1" s="26">
       <c r="J200" s="9" t="inlineStr">
@@ -9841,7 +10147,7 @@
       </c>
       <c r="W200" s="9" t="inlineStr">
         <is>
-          <t>01-启用;02-停用</t>
+          <t>启用、停用</t>
         </is>
       </c>
       <c r="Y200" s="9" t="inlineStr">
@@ -9851,10 +10157,15 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>1. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr"/>
     </row>
     <row r="201" ht="33" customHeight="1" s="26">
       <c r="J201" s="9" t="inlineStr">
@@ -9889,7 +10200,7 @@
       </c>
       <c r="W201" s="9" t="inlineStr">
         <is>
-          <t>01-是;02-否</t>
+          <t>是、否</t>
         </is>
       </c>
       <c r="Y201" s="9" t="inlineStr">
@@ -9904,9 +10215,12 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>代码枚举类字段的'是否枚举'必须为'是'，实际为'否'; '是否枚举'为'否'但枚举值不为空</t>
-        </is>
-      </c>
+          <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
+2. '是否枚举'为'否'但枚举值不为空
+3. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr"/>
     </row>
     <row r="202" ht="33" customHeight="1" s="26">
       <c r="J202" s="9" t="inlineStr">
@@ -9951,6 +10265,7 @@
         </is>
       </c>
       <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr"/>
     </row>
     <row r="203" ht="33" customHeight="1" s="26">
       <c r="J203" s="9" t="inlineStr">
@@ -9995,6 +10310,7 @@
         </is>
       </c>
       <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr"/>
     </row>
     <row r="204" ht="33" customHeight="1" s="26">
       <c r="J204" s="9" t="inlineStr">
@@ -10040,9 +10356,11 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; '是否枚举'为'是'但枚举值为空</t>
-        </is>
-      </c>
+          <t>1. 非代码枚举类/标志类字段的'是否枚举'必须为'否'，实际为'是'
+2. '是否枚举'为'是'但枚举值为空</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr"/>
     </row>
     <row r="205" ht="49.5" customHeight="1" s="26">
       <c r="J205" s="9" t="inlineStr">
@@ -10091,6 +10409,7 @@
         </is>
       </c>
       <c r="AB205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr"/>
     </row>
     <row r="206" ht="66" customHeight="1" s="26">
       <c r="J206" s="9" t="inlineStr">
@@ -10140,9 +10459,11 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>代码枚举类字段的'是否枚举'必须为'是'，实际为'否'; '是否枚举'为'否'但枚举值不为空</t>
-        </is>
-      </c>
+          <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
+2. '是否枚举'为'否'但枚举值不为空</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr"/>
     </row>
     <row r="207" ht="16.5" customHeight="1" s="26">
       <c r="J207" s="9" t="inlineStr">
@@ -10187,6 +10508,7 @@
         </is>
       </c>
       <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr"/>
     </row>
     <row r="208" ht="16.5" customHeight="1" s="26">
       <c r="J208" s="9" t="inlineStr">
@@ -10232,9 +10554,12 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; '是否枚举'为'是'但枚举值为空; 数据示例'托管户余额'不符合域类型'a..(50)'的限制: 包含不允许的字符'托'（字母+特殊符号类不允许数字和汉字）</t>
-        </is>
-      </c>
+          <t>1. 非代码枚举类/标志类字段的'是否枚举'必须为'否'，实际为'是'
+2. '是否枚举'为'是'但枚举值为空
+3. 数据示例'托管户余额'不符合域类型'a..(50)'的限制: 包含不允许的字符'托'（字母+特殊符号类不允许数字和汉字）</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr"/>
     </row>
     <row r="209" ht="33" customHeight="1" s="26">
       <c r="J209" s="9" t="inlineStr">
@@ -10279,14 +10604,11 @@
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'n(1)'格式不合法</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr"/>
     </row>
     <row r="210" ht="33" customHeight="1" s="26">
       <c r="J210" s="9" t="inlineStr">
@@ -10331,14 +10653,11 @@
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'n(1)'格式不合法</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr"/>
+      <c r="AC210" t="inlineStr"/>
     </row>
     <row r="211" ht="33" customHeight="1" s="26">
       <c r="J211" s="9" t="inlineStr">
@@ -10383,14 +10702,11 @@
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'n(1)'格式不合法</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr"/>
     </row>
     <row r="212" ht="33" customHeight="1" s="26">
       <c r="J212" s="9" t="inlineStr">
@@ -10435,14 +10751,11 @@
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'; 域类型'n(1)'格式不合法</t>
-        </is>
-      </c>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
     </row>
     <row r="213" ht="16.5" customHeight="1" s="26">
       <c r="J213" s="9" t="inlineStr">
@@ -10492,9 +10805,10 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>非代码枚举类字段的'是否枚举'必须为'否'，实际为'是'</t>
-        </is>
-      </c>
+          <t>1. 非代码枚举类/标志类字段的'是否枚举'必须为'否'，实际为'是'</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr"/>
     </row>
     <row r="214" ht="16.5" customHeight="1" s="26">
       <c r="J214" s="11" t="inlineStr">
@@ -10539,6 +10853,11 @@
         </is>
       </c>
       <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>因为字段为“补录任务的ID编号”，是用于唯一标识补录任务的编号符号，属于具有特定编码/标识规则的数据项（类似证件号码、机构代码），应归为编码类；填写为文本类不准确，因为其并非说明描述类信息。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="33" customHeight="1" s="26">
       <c r="J215" s="11" t="inlineStr">
@@ -10583,6 +10902,7 @@
         </is>
       </c>
       <c r="AB215" t="inlineStr"/>
+      <c r="AC215" t="inlineStr"/>
     </row>
     <row r="216" ht="16.5" customHeight="1" s="26">
       <c r="J216" s="11" t="inlineStr">
@@ -10627,6 +10947,11 @@
         </is>
       </c>
       <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>因为字段为“根据财汇数据加工生成的公开市场ID”，是用于标识公开市场的编号符号，具有特定的编码/生成规则，应属于编码类；填写为文本类不准确，因为其本质是标识编码而非说明描述类文本。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="33" customHeight="1" s="26">
       <c r="J217" s="11" t="inlineStr">
@@ -10672,9 +10997,10 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>域类型'n(30)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'n(30)'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr"/>
     </row>
     <row r="218" ht="49.5" customHeight="1" s="26">
       <c r="J218" s="11" t="inlineStr">
@@ -10719,10 +11045,15 @@
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'交易类型标志'与业务含义'记录本条记录的交易类型'在语义上完全等价，只是换了一种说法（把'标志'改为'记录...的交易类型'），未补充交易类型的具体种类、标志取值含义或业务背景等任何新信息，属于语义重复，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr"/>
     </row>
     <row r="219" ht="33" customHeight="1" s="26">
       <c r="J219" s="11" t="inlineStr">
@@ -10768,9 +11099,10 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>域类型'i(17.0)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'i(17.0)'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr"/>
     </row>
     <row r="220" ht="33" customHeight="1" s="26">
       <c r="J220" s="11" t="inlineStr">
@@ -10816,9 +11148,11 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>域类型'n(1)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 标志类字段的'是否枚举'必须为'是'，实际为'否'
+2. 字段中文名'还款交易是否做了还款还原标志'与业务含义'还款交易是否做了还款还原'在语义上完全相同，业务含义仅删去了'标志'二字，未增加任何解释、背景或取值说明，属于简单删词改写，未提供实质信息，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr"/>
     </row>
     <row r="221" ht="82.5" customHeight="1" s="26">
       <c r="J221" s="11" t="inlineStr">
@@ -10853,7 +11187,7 @@
       </c>
       <c r="W221" s="11" t="inlineStr">
         <is>
-          <t>0000-“产品到期日”、“产品到期资金到账天数”都一致；;0001-仅“产品到期日”对平；;0002-仅“产品到期资金到账天数”对平;0003-未核对</t>
+          <t>0000-“产品到期日”、“产品到期资金到账天数”都一致;0001-仅“产品到期日”对平;0002-仅“产品到期资金到账天数”对平;0003-未核对</t>
         </is>
       </c>
       <c r="Y221" s="11" t="inlineStr">
@@ -10867,6 +11201,7 @@
         </is>
       </c>
       <c r="AB221" t="inlineStr"/>
+      <c r="AC221" t="inlineStr"/>
     </row>
     <row r="222" ht="33" customHeight="1" s="26">
       <c r="J222" s="11" t="inlineStr">
@@ -10912,9 +11247,11 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>域类型'i(20.4)'格式不合法; 字段中文名'1001银行存款'包含科目代码'1001'，代码部分不具有自解释性，不属于完全见名知意的常见名称。业务含义'1001银行存款'与字段中文名完全相同，属于完全复制，未对代码或字段含义做任何解释，未提供实质信息，无效。</t>
-        </is>
-      </c>
+          <t>1. 域类型'i(20.4)'格式不合法
+2. 字段中文名'1001银行存款'与业务含义完全相同，属于完全复制。字段名中的'1001'是会计科目编码，字段名本身并非充分自明（编码含义未体现），而业务含义未对编码或字段含义做任何解释，未提供任何新增信息，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr"/>
     </row>
     <row r="223" ht="33" customHeight="1" s="26">
       <c r="J223" s="11" t="inlineStr">
@@ -10960,9 +11297,11 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>域类型'i(20.4)'格式不合法; 字段中文名'1204.01银行存款应收利息'包含科目代码'1204.01'，代码部分不具有自解释性，不属于完全见名知意的常见名称。业务含义'1204.01银行存款应收利息'与字段中文名完全相同，属于完全复制，未对代码或字段含义做任何解释，未提供实质信息，无效。</t>
-        </is>
-      </c>
+          <t>1. 域类型'i(20.4)'格式不合法
+2. 字段中文名'1204.01银行存款应收利息'与业务含义完全相同，属于完全复制。字段名中的'1204.01'是会计科目编码，字段名本身不能完全自明，业务含义也未对编码或'应收利息'的具体含义做任何说明，未提供实质信息，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr"/>
     </row>
     <row r="224" ht="16.5" customHeight="1" s="26">
       <c r="J224" s="11" t="inlineStr">
@@ -11008,9 +11347,11 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>数据示例'投资管理部...'不符合域类型'an..(50)'的限制: 包含汉字字符'投'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'投资管理部...'不符合域类型'an..(50)'的限制: 包含汉字字符'投'（数字+字母+特殊符号类不允许汉字）
+2. 字段中文名'归属管理部门'的业务含义'指数因子-归属管理部门'只是在原名称前机械添加类别前缀'指数因子-'，未解释归属管理部门的具体含义、用途或业务背景，属于简单加词，未提供实质信息，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr"/>
     </row>
     <row r="225" ht="16.5" customHeight="1" s="26">
       <c r="J225" s="11" t="inlineStr">
@@ -11056,9 +11397,11 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>域类型'i(28.14)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'i(28.14)'格式不合法
+2. 字段中文名'指数行情'的业务含义'指数因子-指数行情'只是在原名称前机械添加'指数因子-'前缀，未对指数行情的具体含义、内容或用途做任何实质描述，属于简单加词，未提供新增信息，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr"/>
     </row>
     <row r="226" ht="16.5" customHeight="1" s="26">
       <c r="J226" s="11" t="inlineStr">
@@ -11099,10 +11442,15 @@
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB226" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'二级类别后缀'的业务含义'指数因子-二级类别后缀'只是在原名称前机械添加'指数因子-'前缀，未解释二级类别后缀的具体含义或使用场景，属于简单加词，未提供实质信息，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr"/>
     </row>
     <row r="227" ht="16.5" customHeight="1" s="26">
       <c r="J227" s="11" t="inlineStr">
@@ -11147,6 +11495,7 @@
         </is>
       </c>
       <c r="AB227" t="inlineStr"/>
+      <c r="AC227" t="inlineStr"/>
     </row>
     <row r="228" ht="33" customHeight="1" s="26">
       <c r="J228" s="11" t="inlineStr">
@@ -11195,6 +11544,7 @@
         </is>
       </c>
       <c r="AB228" t="inlineStr"/>
+      <c r="AC228" t="inlineStr"/>
     </row>
     <row r="229" ht="49.5" customHeight="1" s="26">
       <c r="J229" s="11" t="inlineStr">
@@ -11243,6 +11593,7 @@
         </is>
       </c>
       <c r="AB229" t="inlineStr"/>
+      <c r="AC229" t="inlineStr"/>
     </row>
     <row r="230" ht="33" customHeight="1" s="26">
       <c r="J230" s="9" t="inlineStr">
@@ -11287,6 +11638,7 @@
         </is>
       </c>
       <c r="AB230" t="inlineStr"/>
+      <c r="AC230" t="inlineStr"/>
     </row>
     <row r="231" ht="49.5" customHeight="1" s="26">
       <c r="J231" s="9" t="inlineStr">
@@ -11335,6 +11687,7 @@
         </is>
       </c>
       <c r="AB231" t="inlineStr"/>
+      <c r="AC231" t="inlineStr"/>
     </row>
     <row r="232" ht="49.5" customHeight="1" s="26">
       <c r="J232" s="9" t="inlineStr">
@@ -11383,6 +11736,7 @@
         </is>
       </c>
       <c r="AB232" t="inlineStr"/>
+      <c r="AC232" t="inlineStr"/>
     </row>
     <row r="233" ht="33" customHeight="1" s="26">
       <c r="J233" s="9" t="inlineStr">
@@ -11427,6 +11781,7 @@
         </is>
       </c>
       <c r="AB233" t="inlineStr"/>
+      <c r="AC233" t="inlineStr"/>
     </row>
     <row r="234" ht="396" customHeight="1" s="26">
       <c r="J234" s="9" t="inlineStr">
@@ -11475,6 +11830,7 @@
         </is>
       </c>
       <c r="AB234" t="inlineStr"/>
+      <c r="AC234" t="inlineStr"/>
     </row>
     <row r="235" ht="33" customHeight="1" s="26">
       <c r="J235" s="9" t="inlineStr">
@@ -11523,6 +11879,7 @@
         </is>
       </c>
       <c r="AB235" t="inlineStr"/>
+      <c r="AC235" t="inlineStr"/>
     </row>
     <row r="236" ht="16.5" customHeight="1" s="26">
       <c r="J236" s="9" t="inlineStr">
@@ -11568,9 +11925,10 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>字段中文名'规则调用点代码'在表'产品销售文件模板表'中重复</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'规则调用点代码'在表'产品销售文件模板表'中重复</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr"/>
     </row>
     <row r="237" ht="16.5" customHeight="1" s="26">
       <c r="J237" s="9" t="inlineStr">
@@ -11616,9 +11974,11 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>代码枚举类字段的'是否枚举'必须为'是'，实际为'否'; 字段中文名'产品模板类型'在表'产品销售文件模板表'中重复</t>
-        </is>
-      </c>
+          <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
+2. 字段中文名'产品模板类型'在表'产品销售文件模板表'中重复</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr"/>
     </row>
     <row r="238" ht="16.5" customHeight="1" s="26">
       <c r="J238" s="9" t="inlineStr">
@@ -11664,9 +12024,11 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>代码枚举类字段的'是否枚举'必须为'是'，实际为'否'; 字段中文名'产品类型'在表'产品销售文件模板表'中重复</t>
-        </is>
-      </c>
+          <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
+2. 字段中文名'产品类型'在表'产品销售文件模板表'中重复</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr"/>
     </row>
     <row r="239" ht="16.5" customHeight="1" s="26">
       <c r="J239" s="9" t="inlineStr">
@@ -11712,9 +12074,11 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>代码枚举类字段的'是否枚举'必须为'是'，实际为'否'; 字段中文名'操作类型'在表'产品销售文件模板表'中重复</t>
-        </is>
-      </c>
+          <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
+2. 字段中文名'操作类型'在表'产品销售文件模板表'中重复</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr"/>
     </row>
     <row r="240" ht="16.5" customHeight="1" s="26">
       <c r="J240" s="9" t="inlineStr">
@@ -11760,9 +12124,11 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>代码枚举类字段的'是否枚举'必须为'是'，实际为'否'; 字段中文名'模板状态'在表'产品销售文件模板表'中重复</t>
-        </is>
-      </c>
+          <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
+2. 字段中文名'模板状态'在表'产品销售文件模板表'中重复</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr"/>
     </row>
     <row r="241" ht="16.5" customHeight="1" s="26">
       <c r="J241" s="9" t="inlineStr">
@@ -11808,9 +12174,10 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>字段中文名'更新人员工号'在表'产品申报登记信息表'中重复</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'更新人员工号'在表'产品申报登记信息表'中重复</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr"/>
     </row>
     <row r="242" ht="16.5" customHeight="1" s="26">
       <c r="J242" s="9" t="inlineStr">
@@ -11856,9 +12223,10 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>字段中文名'附件后缀'在表'产品申报登记附件表'中重复</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'附件后缀'在表'产品申报登记附件表'中重复</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr"/>
     </row>
     <row r="243" ht="16.5" customHeight="1" s="26">
       <c r="J243" s="9" t="inlineStr">
@@ -11904,9 +12272,10 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>字段中文名'规则调用点代码'在表'产品销售文件模板表'中重复</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'规则调用点代码'在表'产品销售文件模板表'中重复</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr"/>
     </row>
     <row r="244" ht="16.5" customHeight="1" s="26">
       <c r="J244" s="9" t="inlineStr">
@@ -11952,9 +12321,11 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>代码枚举类字段的'是否枚举'必须为'是'，实际为'否'; 字段中文名'产品模板类型'在表'产品销售文件模板表'中重复</t>
-        </is>
-      </c>
+          <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
+2. 字段中文名'产品模板类型'在表'产品销售文件模板表'中重复</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr"/>
     </row>
     <row r="245" ht="16.5" customHeight="1" s="26">
       <c r="J245" s="9" t="inlineStr">
@@ -12000,9 +12371,11 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>代码枚举类字段的'是否枚举'必须为'是'，实际为'否'; 字段中文名'产品类型'在表'产品销售文件模板表'中重复</t>
-        </is>
-      </c>
+          <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
+2. 字段中文名'产品类型'在表'产品销售文件模板表'中重复</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr"/>
     </row>
     <row r="246" ht="16.5" customHeight="1" s="26">
       <c r="J246" s="9" t="inlineStr">
@@ -12048,9 +12421,11 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>代码枚举类字段的'是否枚举'必须为'是'，实际为'否'; 字段中文名'操作类型'在表'产品销售文件模板表'中重复</t>
-        </is>
-      </c>
+          <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
+2. 字段中文名'操作类型'在表'产品销售文件模板表'中重复</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr"/>
     </row>
     <row r="247" ht="16.5" customHeight="1" s="26">
       <c r="J247" s="9" t="inlineStr">
@@ -12096,9 +12471,11 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>代码枚举类字段的'是否枚举'必须为'是'，实际为'否'; 字段中文名'模板状态'在表'产品销售文件模板表'中重复</t>
-        </is>
-      </c>
+          <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
+2. 字段中文名'模板状态'在表'产品销售文件模板表'中重复</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr"/>
     </row>
     <row r="248" ht="16.5" customHeight="1" s="26">
       <c r="J248" s="9" t="inlineStr">
@@ -12144,9 +12521,10 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>字段中文名'更新人员工号'在表'产品申报登记信息表'中重复</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'更新人员工号'在表'产品申报登记信息表'中重复</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr"/>
     </row>
     <row r="249" ht="16.5" customHeight="1" s="26">
       <c r="J249" s="9" t="inlineStr">
@@ -12192,9 +12570,10 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>字段中文名'附件后缀'在表'产品申报登记附件表'中重复</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'附件后缀'在表'产品申报登记附件表'中重复</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr"/>
     </row>
     <row r="250" ht="49.5" customHeight="1" s="26">
       <c r="J250" s="9" t="inlineStr">
@@ -12243,6 +12622,7 @@
         </is>
       </c>
       <c r="AB250" t="inlineStr"/>
+      <c r="AC250" t="inlineStr"/>
     </row>
     <row r="251" ht="16.5" customHeight="1" s="26">
       <c r="J251" s="9" t="inlineStr">
@@ -12287,6 +12667,7 @@
         </is>
       </c>
       <c r="AB251" t="inlineStr"/>
+      <c r="AC251" t="inlineStr"/>
     </row>
     <row r="252" ht="33" customHeight="1" s="26">
       <c r="J252" s="9" t="inlineStr">
@@ -12335,6 +12716,7 @@
         </is>
       </c>
       <c r="AB252" t="inlineStr"/>
+      <c r="AC252" t="inlineStr"/>
     </row>
     <row r="253" ht="33" customHeight="1" s="26">
       <c r="J253" s="9" t="inlineStr">
@@ -12383,6 +12765,7 @@
         </is>
       </c>
       <c r="AB253" t="inlineStr"/>
+      <c r="AC253" t="inlineStr"/>
     </row>
     <row r="254" ht="16.5" customHeight="1" s="26">
       <c r="J254" s="9" t="inlineStr">
@@ -12427,6 +12810,11 @@
         </is>
       </c>
       <c r="AB254" t="inlineStr"/>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>因为字段“所有节点意向度”表示客户/节点的意向程度，通常以明确分类的等级（如高、中、低或A/B/C等）表示，属于有明确分类分组的取值，应归为代码枚举类；填写为文本类不准确，因为其并非自由描述的文本信息。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="33" customHeight="1" s="26">
       <c r="J255" s="9" t="inlineStr">
@@ -12475,6 +12863,7 @@
         </is>
       </c>
       <c r="AB255" t="inlineStr"/>
+      <c r="AC255" t="inlineStr"/>
     </row>
     <row r="256" ht="33" customHeight="1" s="26">
       <c r="J256" s="9" t="inlineStr">
@@ -12519,6 +12908,7 @@
         </is>
       </c>
       <c r="AB256" t="inlineStr"/>
+      <c r="AC256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="J257" s="14" t="inlineStr">
@@ -12563,6 +12953,7 @@
         </is>
       </c>
       <c r="AB257" t="inlineStr"/>
+      <c r="AC257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="J258" s="14" t="inlineStr">
@@ -12607,6 +12998,11 @@
         </is>
       </c>
       <c r="AB258" t="inlineStr"/>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>因为字段名为"业务类型"，本质是标识外呼名单所属业务类型的分类/类别，属于典型的类型类数据项（类型、种类、模式等）。虽然业务定义中提及"编码"，但该字段语义是对业务类型进行分类取值，而非具有固定编码规则的编号，按分类应属于代码枚举类，填写为编码类不准确。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="J259" s="14" t="inlineStr">
@@ -12651,6 +13047,7 @@
         </is>
       </c>
       <c r="AB259" t="inlineStr"/>
+      <c r="AC259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="J260" s="14" t="inlineStr">
@@ -12699,6 +13096,7 @@
         </is>
       </c>
       <c r="AB260" t="inlineStr"/>
+      <c r="AC260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="J261" s="14" t="inlineStr">
@@ -12743,6 +13141,11 @@
         </is>
       </c>
       <c r="AB261" t="inlineStr"/>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>因为"主叫号码"是进行外呼时的外显电话号码，电话号码属于说明描述类信息。字段类型解释中明确将"电话号码"作为文本类的示例，应属于文本类，而非具有特定编码规则的编码类。，当前字段所属类型可能错误，应为文本类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="27" customHeight="1" s="26">
       <c r="J262" s="14" t="inlineStr">
@@ -12787,6 +13190,7 @@
         </is>
       </c>
       <c r="AB262" t="inlineStr"/>
+      <c r="AC262" t="inlineStr"/>
     </row>
     <row r="263" ht="27" customHeight="1" s="26">
       <c r="J263" s="14" t="inlineStr">
@@ -12831,6 +13235,7 @@
         </is>
       </c>
       <c r="AB263" t="inlineStr"/>
+      <c r="AC263" t="inlineStr"/>
     </row>
     <row r="264" ht="27" customHeight="1" s="26">
       <c r="J264" s="14" t="inlineStr">
@@ -12875,6 +13280,11 @@
         </is>
       </c>
       <c r="AB264" t="inlineStr"/>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>因为"意向度结果"表示最后命中的意向度，通常为高/中/低等明确的等级分类取值，属于有明确分类、分组的数据项，应按代码枚举类归类；填写为文本类不准确。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="J265" s="14" t="inlineStr">
@@ -12919,6 +13329,7 @@
         </is>
       </c>
       <c r="AB265" t="inlineStr"/>
+      <c r="AC265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="J266" s="14" t="inlineStr">
@@ -12963,6 +13374,7 @@
         </is>
       </c>
       <c r="AB266" t="inlineStr"/>
+      <c r="AC266" t="inlineStr"/>
     </row>
     <row r="267" ht="27" customHeight="1" s="26">
       <c r="J267" s="14" t="inlineStr">
@@ -13007,6 +13419,7 @@
         </is>
       </c>
       <c r="AB267" t="inlineStr"/>
+      <c r="AC267" t="inlineStr"/>
     </row>
     <row r="268" ht="27" customHeight="1" s="26">
       <c r="J268" s="14" t="inlineStr">
@@ -13051,6 +13464,7 @@
         </is>
       </c>
       <c r="AB268" t="inlineStr"/>
+      <c r="AC268" t="inlineStr"/>
     </row>
     <row r="269" ht="27" customHeight="1" s="26">
       <c r="J269" s="14" t="inlineStr">
@@ -13095,6 +13509,7 @@
         </is>
       </c>
       <c r="AB269" t="inlineStr"/>
+      <c r="AC269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="J270" s="14" t="inlineStr">
@@ -13139,6 +13554,7 @@
         </is>
       </c>
       <c r="AB270" t="inlineStr"/>
+      <c r="AC270" t="inlineStr"/>
     </row>
     <row r="271" ht="27" customHeight="1" s="26">
       <c r="J271" s="14" t="inlineStr">
@@ -13183,6 +13599,7 @@
         </is>
       </c>
       <c r="AB271" t="inlineStr"/>
+      <c r="AC271" t="inlineStr"/>
     </row>
     <row r="272" ht="27" customHeight="1" s="26">
       <c r="J272" s="14" t="inlineStr">
@@ -13227,6 +13644,7 @@
         </is>
       </c>
       <c r="AB272" t="inlineStr"/>
+      <c r="AC272" t="inlineStr"/>
     </row>
     <row r="273" ht="27" customHeight="1" s="26">
       <c r="J273" s="14" t="inlineStr">
@@ -13271,6 +13689,7 @@
         </is>
       </c>
       <c r="AB273" t="inlineStr"/>
+      <c r="AC273" t="inlineStr"/>
     </row>
     <row r="274" ht="27" customHeight="1" s="26">
       <c r="J274" s="14" t="inlineStr">
@@ -13315,6 +13734,7 @@
         </is>
       </c>
       <c r="AB274" t="inlineStr"/>
+      <c r="AC274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="J275" s="14" t="inlineStr">
@@ -13359,6 +13779,7 @@
         </is>
       </c>
       <c r="AB275" t="inlineStr"/>
+      <c r="AC275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="J276" s="14" t="inlineStr">
@@ -13403,6 +13824,7 @@
         </is>
       </c>
       <c r="AB276" t="inlineStr"/>
+      <c r="AC276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="J277" s="14" t="inlineStr">
@@ -13447,6 +13869,7 @@
         </is>
       </c>
       <c r="AB277" t="inlineStr"/>
+      <c r="AC277" t="inlineStr"/>
     </row>
     <row r="278" ht="33" customHeight="1" s="26">
       <c r="J278" s="15" t="inlineStr">
@@ -13491,6 +13914,7 @@
         </is>
       </c>
       <c r="AB278" t="inlineStr"/>
+      <c r="AC278" t="inlineStr"/>
     </row>
     <row r="279" ht="33" customHeight="1" s="26">
       <c r="J279" s="15" t="inlineStr">
@@ -13535,6 +13959,11 @@
         </is>
       </c>
       <c r="AB279" t="inlineStr"/>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>因为通话标识是根据时间戳生成、用于唯一标识一通外呼通话的标识符，属于具有一定生成规则、便于计算机识别的标识符号，而非普通说明描述文本，应属于编码类而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="16.5" customHeight="1" s="26">
       <c r="J280" s="15" t="inlineStr">
@@ -13579,6 +14008,11 @@
         </is>
       </c>
       <c r="AB280" t="inlineStr"/>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>因为运营商名称取值是有限的固定集合（如移动、联通、电信），具有明确分类、分组、多取值的特征，属于代码枚举类而非一般性的文本描述信息。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="16.5" customHeight="1" s="26">
       <c r="J281" s="15" t="inlineStr">
@@ -13623,6 +14057,11 @@
         </is>
       </c>
       <c r="AB281" t="inlineStr"/>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>因为记录编号是外呼记录表的自增主键，作为唯一标识记录的编号符号，具有自增的规律性规则，主要作用是标识而非数量统计，应属于编码类而非数值类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="16.5" customHeight="1" s="26">
       <c r="J282" s="15" t="inlineStr">
@@ -13667,6 +14106,7 @@
         </is>
       </c>
       <c r="AB282" t="inlineStr"/>
+      <c r="AC282" t="inlineStr"/>
     </row>
     <row r="283" ht="16.5" customHeight="1" s="26">
       <c r="J283" s="15" t="inlineStr">
@@ -13711,6 +14151,7 @@
         </is>
       </c>
       <c r="AB283" t="inlineStr"/>
+      <c r="AC283" t="inlineStr"/>
     </row>
     <row r="284" ht="33" customHeight="1" s="26">
       <c r="J284" s="15" t="inlineStr">
@@ -13759,6 +14200,7 @@
         </is>
       </c>
       <c r="AB284" t="inlineStr"/>
+      <c r="AC284" t="inlineStr"/>
     </row>
     <row r="285" ht="16.5" customHeight="1" s="26">
       <c r="J285" s="15" t="inlineStr">
@@ -13807,6 +14249,7 @@
         </is>
       </c>
       <c r="AB285" t="inlineStr"/>
+      <c r="AC285" t="inlineStr"/>
     </row>
     <row r="286" ht="33" customHeight="1" s="26">
       <c r="J286" s="15" t="inlineStr">
@@ -13851,6 +14294,7 @@
         </is>
       </c>
       <c r="AB286" t="inlineStr"/>
+      <c r="AC286" t="inlineStr"/>
     </row>
     <row r="287" ht="33" customHeight="1" s="26">
       <c r="J287" s="15" t="inlineStr">
@@ -13896,9 +14340,10 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>域类型'TIMESTAMP(0)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'TIMESTAMP(0)'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr"/>
     </row>
     <row r="288" ht="33" customHeight="1" s="26">
       <c r="J288" s="15" t="inlineStr">
@@ -13943,6 +14388,7 @@
         </is>
       </c>
       <c r="AB288" t="inlineStr"/>
+      <c r="AC288" t="inlineStr"/>
     </row>
     <row r="289" ht="33" customHeight="1" s="26">
       <c r="J289" s="15" t="inlineStr">
@@ -13991,6 +14437,7 @@
         </is>
       </c>
       <c r="AB289" t="inlineStr"/>
+      <c r="AC289" t="inlineStr"/>
     </row>
     <row r="290" ht="33" customHeight="1" s="26">
       <c r="J290" s="15" t="inlineStr">
@@ -14035,6 +14482,7 @@
         </is>
       </c>
       <c r="AB290" t="inlineStr"/>
+      <c r="AC290" t="inlineStr"/>
     </row>
     <row r="291" ht="16.5" customHeight="1" s="26">
       <c r="J291" s="15" t="inlineStr">
@@ -14079,6 +14527,7 @@
         </is>
       </c>
       <c r="AB291" t="inlineStr"/>
+      <c r="AC291" t="inlineStr"/>
     </row>
     <row r="292" ht="16.5" customHeight="1" s="26">
       <c r="J292" s="15" t="inlineStr">
@@ -14123,6 +14572,7 @@
         </is>
       </c>
       <c r="AB292" t="inlineStr"/>
+      <c r="AC292" t="inlineStr"/>
     </row>
     <row r="293" ht="33" customHeight="1" s="26">
       <c r="J293" s="15" t="inlineStr">
@@ -14168,9 +14618,10 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>域类型'i(9)'不允许用于字段所属类型'编码类'</t>
-        </is>
-      </c>
+          <t>1. 域类型'i(9)'不允许用于字段所属类型'编码类'</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr"/>
     </row>
     <row r="294" ht="33" customHeight="1" s="26">
       <c r="J294" s="15" t="inlineStr">
@@ -14216,9 +14667,10 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>域类型'i(9)'不允许用于字段所属类型'编码类'</t>
-        </is>
-      </c>
+          <t>1. 域类型'i(9)'不允许用于字段所属类型'编码类'</t>
+        </is>
+      </c>
+      <c r="AC294" t="inlineStr"/>
     </row>
     <row r="295" ht="16.5" customHeight="1" s="26">
       <c r="J295" s="15" t="inlineStr">
@@ -14261,6 +14713,7 @@
         </is>
       </c>
       <c r="AB295" t="inlineStr"/>
+      <c r="AC295" t="inlineStr"/>
     </row>
     <row r="296" ht="16.5" customHeight="1" s="26">
       <c r="J296" s="15" t="inlineStr">
@@ -14303,6 +14756,7 @@
         </is>
       </c>
       <c r="AB296" t="inlineStr"/>
+      <c r="AC296" t="inlineStr"/>
     </row>
     <row r="297" ht="16.5" customHeight="1" s="26">
       <c r="J297" s="15" t="inlineStr">
@@ -14345,6 +14799,7 @@
         </is>
       </c>
       <c r="AB297" t="inlineStr"/>
+      <c r="AC297" t="inlineStr"/>
     </row>
     <row r="298" ht="16.5" customFormat="1" customHeight="1" s="17">
       <c r="J298" s="9" t="inlineStr">
@@ -14390,9 +14845,10 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>数据示例'限呼原因'不符合域类型'an..(300)'的限制: 包含汉字字符'限'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'限呼原因'不符合域类型'an..(300)'的限制: 包含汉字字符'限'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr"/>
     </row>
     <row r="299" ht="16.5" customFormat="1" customHeight="1" s="17">
       <c r="J299" s="9" t="inlineStr">
@@ -14438,9 +14894,10 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>数据示例'限呼删除原因'不符合域类型'an..(300)'的限制: 包含汉字字符'限'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'限呼删除原因'不符合域类型'an..(300)'的限制: 包含汉字字符'限'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr"/>
     </row>
     <row r="300" ht="165" customHeight="1" s="26">
       <c r="J300" s="9" t="inlineStr">
@@ -14489,6 +14946,7 @@
         </is>
       </c>
       <c r="AB300" t="inlineStr"/>
+      <c r="AC300" t="inlineStr"/>
     </row>
     <row r="301" ht="16.5" customHeight="1" s="26">
       <c r="J301" s="9" t="inlineStr">
@@ -14533,6 +14991,7 @@
         </is>
       </c>
       <c r="AB301" t="inlineStr"/>
+      <c r="AC301" t="inlineStr"/>
     </row>
     <row r="302" ht="16.5" customHeight="1" s="26">
       <c r="J302" s="9" t="inlineStr">
@@ -14578,9 +15037,10 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>数据示例'失败原因'不符合域类型'an..(100)'的限制: 包含汉字字符'失'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'失败原因'不符合域类型'an..(100)'的限制: 包含汉字字符'失'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr"/>
     </row>
     <row r="303" ht="16.5" customHeight="1" s="26">
       <c r="J303" s="9" t="inlineStr">
@@ -14626,9 +15086,10 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>数据示例'EMail模板内容'不符合域类型'an..(50)'的限制: 包含汉字字符'模'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'EMail模板内容'不符合域类型'an..(50)'的限制: 包含汉字字符'模'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC303" t="inlineStr"/>
     </row>
     <row r="304" ht="16.5" customHeight="1" s="26">
       <c r="J304" s="9" t="inlineStr">
@@ -14674,9 +15135,10 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>数据示例'信函模板内容'不符合域类型'an..(50)'的限制: 包含汉字字符'信'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'信函模板内容'不符合域类型'an..(50)'的限制: 包含汉字字符'信'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr"/>
     </row>
     <row r="305" ht="16.5" customHeight="1" s="26">
       <c r="J305" s="9" t="inlineStr">
@@ -14722,9 +15184,10 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>数据示例'分公司'不符合域类型'an..(200)'的限制: 包含汉字字符'分'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'分公司'不符合域类型'an..(200)'的限制: 包含汉字字符'分'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr"/>
     </row>
     <row r="306" ht="16.5" customHeight="1" s="26">
       <c r="J306" s="9" t="inlineStr">
@@ -14770,9 +15233,10 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>数据示例'上海催收机构'不符合域类型'an..(20)'的限制: 包含汉字字符'上'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'上海催收机构'不符合域类型'an..(20)'的限制: 包含汉字字符'上'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC306" t="inlineStr"/>
     </row>
     <row r="307" ht="33" customHeight="1" s="26">
       <c r="J307" s="9" t="inlineStr">
@@ -14817,6 +15281,7 @@
         </is>
       </c>
       <c r="AB307" t="inlineStr"/>
+      <c r="AC307" t="inlineStr"/>
     </row>
     <row r="308" ht="33" customHeight="1" s="26">
       <c r="J308" s="9" t="inlineStr">
@@ -14861,6 +15326,7 @@
         </is>
       </c>
       <c r="AB308" t="inlineStr"/>
+      <c r="AC308" t="inlineStr"/>
     </row>
     <row r="309" ht="16.5" customHeight="1" s="26">
       <c r="J309" s="9" t="inlineStr">
@@ -14906,9 +15372,11 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>数据示例'电子律师函模板内容'不符合域类型'an..(60)'的限制: 包含汉字字符'电'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'电子律师函模板内容'不符合域类型'an..(60)'的限制: 包含汉字字符'电'（数字+字母+特殊符号类不允许汉字）
+2. 字段中文名'电子律师函模板'与业务含义'电子律师函模板'完全相同，属于完全复制。'电子律师函模板'并非像'客户名称'、'开户日期'那样常见的见名知意金融名称，业务含义未对字段名进行任何解释或补充，未提供额外信息，判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr"/>
     </row>
     <row r="310" ht="16.5" customHeight="1" s="26">
       <c r="J310" s="9" t="inlineStr">
@@ -14953,6 +15421,11 @@
         </is>
       </c>
       <c r="AB310" t="inlineStr"/>
+      <c r="AC310" t="inlineStr">
+        <is>
+          <t>因为行动类型表示电子律师函提醒/查询短信行动流水行动的类型，属于有明确分类、多取值的类型字段（如提醒、查询等），应属于代码枚举类，而非文本类。文本类适用于说明描述类信息，行动类型是枚举取值，故填写为文本类可能错误。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="16.5" customHeight="1" s="26">
       <c r="J311" s="9" t="inlineStr">
@@ -14998,9 +15471,10 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>数据示例'转结案'不符合域类型'an..(100)'的限制: 包含汉字字符'转'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'转结案'不符合域类型'an..(100)'的限制: 包含汉字字符'转'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr"/>
     </row>
     <row r="312" ht="33" customHeight="1" s="26">
       <c r="J312" s="9" t="inlineStr">
@@ -15046,9 +15520,10 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>数据示例'记录人名称'不符合域类型'an..(50)'的限制: 包含汉字字符'记'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'记录人名称'不符合域类型'an..(50)'的限制: 包含汉字字符'记'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC312" t="inlineStr"/>
     </row>
     <row r="313" ht="33" customHeight="1" s="26">
       <c r="J313" s="9" t="inlineStr">
@@ -15091,6 +15566,7 @@
         </is>
       </c>
       <c r="AB313" t="inlineStr"/>
+      <c r="AC313" t="inlineStr"/>
     </row>
     <row r="314" ht="16.5" customHeight="1" s="26">
       <c r="J314" s="9" t="inlineStr">
@@ -15125,7 +15601,7 @@
       </c>
       <c r="W314" s="9" t="inlineStr">
         <is>
-          <t>01-单人巡航模式;02-机器人模式</t>
+          <t>单人巡航模式/机器人模式</t>
         </is>
       </c>
       <c r="Y314" s="9" t="inlineStr">
@@ -15135,10 +15611,15 @@
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB314" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>1. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr"/>
     </row>
     <row r="315" ht="16.5" customHeight="1" s="26">
       <c r="J315" s="9" t="inlineStr">
@@ -15184,9 +15665,10 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>数据示例'本人'不符合域类型'an..(50)'的限制: 包含汉字字符'本'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'本人'不符合域类型'an..(50)'的限制: 包含汉字字符'本'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr"/>
     </row>
     <row r="316" ht="16.5" customHeight="1" s="26">
       <c r="J316" s="9" t="inlineStr">
@@ -15232,9 +15714,10 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>数据示例'振铃'不符合域类型'an..(50)'的限制: 包含汉字字符'振'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'振铃'不符合域类型'an..(50)'的限制: 包含汉字字符'振'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr"/>
     </row>
     <row r="317" ht="33" customHeight="1" s="26">
       <c r="J317" s="9" t="inlineStr">
@@ -15277,6 +15760,7 @@
         </is>
       </c>
       <c r="AB317" t="inlineStr"/>
+      <c r="AC317" t="inlineStr"/>
     </row>
     <row r="318" ht="16.5" customHeight="1" s="26">
       <c r="J318" s="9" t="inlineStr">
@@ -15321,6 +15805,7 @@
         </is>
       </c>
       <c r="AB318" t="inlineStr"/>
+      <c r="AC318" t="inlineStr"/>
     </row>
     <row r="319" ht="33" customHeight="1" s="26">
       <c r="J319" s="9" t="inlineStr">
@@ -15363,6 +15848,7 @@
         </is>
       </c>
       <c r="AB319" t="inlineStr"/>
+      <c r="AC319" t="inlineStr"/>
     </row>
     <row r="320" ht="33" customHeight="1" s="26">
       <c r="J320" s="9" t="inlineStr">
@@ -15412,9 +15898,10 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
-        </is>
-      </c>
+          <t>1. 枚举值有且仅有'是'和'否'两项，该字段应为标志类而非代码枚举类</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr"/>
     </row>
     <row r="321" ht="16.5" customHeight="1" s="26">
       <c r="J321" s="9" t="inlineStr">
@@ -15459,6 +15946,7 @@
         </is>
       </c>
       <c r="AB321" t="inlineStr"/>
+      <c r="AC321" t="inlineStr"/>
     </row>
     <row r="322" ht="16.5" customHeight="1" s="26">
       <c r="J322" s="9" t="inlineStr">
@@ -15504,9 +15992,10 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>数据示例'因某原因复议'不符合域类型'an..(200)'的限制: 包含汉字字符'因'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'因某原因复议'不符合域类型'an..(200)'的限制: 包含汉字字符'因'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr"/>
     </row>
     <row r="323" ht="16.5" customHeight="1" s="26">
       <c r="J323" s="9" t="inlineStr">
@@ -15541,7 +16030,7 @@
       </c>
       <c r="W323" s="9" t="inlineStr">
         <is>
-          <t>01-电催特殊案件;02-直催问题质检</t>
+          <t>电催特殊案件、直催问题质检</t>
         </is>
       </c>
       <c r="Y323" s="9" t="inlineStr">
@@ -15551,10 +16040,15 @@
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB323" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>1. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr"/>
     </row>
     <row r="324" ht="16.5" customHeight="1" s="26">
       <c r="J324" s="9" t="inlineStr">
@@ -15599,6 +16093,7 @@
         </is>
       </c>
       <c r="AB324" t="inlineStr"/>
+      <c r="AC324" t="inlineStr"/>
     </row>
     <row r="325" ht="16.5" customHeight="1" s="26">
       <c r="J325" s="9" t="inlineStr">
@@ -15644,9 +16139,10 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>数据示例'张三'不符合域类型'an..(20)'的限制: 包含汉字字符'张'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'张三'不符合域类型'an..(20)'的限制: 包含汉字字符'张'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr"/>
     </row>
     <row r="326" ht="16.5" customHeight="1" s="26">
       <c r="J326" s="9" t="inlineStr">
@@ -15691,6 +16187,7 @@
         </is>
       </c>
       <c r="AB326" t="inlineStr"/>
+      <c r="AC326" t="inlineStr"/>
     </row>
     <row r="327" ht="16.5" customHeight="1" s="26">
       <c r="J327" s="9" t="inlineStr">
@@ -15735,6 +16232,7 @@
         </is>
       </c>
       <c r="AB327" t="inlineStr"/>
+      <c r="AC327" t="inlineStr"/>
     </row>
     <row r="328" ht="33" customHeight="1" s="26">
       <c r="J328" s="9" t="inlineStr">
@@ -15777,6 +16275,7 @@
         </is>
       </c>
       <c r="AB328" t="inlineStr"/>
+      <c r="AC328" t="inlineStr"/>
     </row>
     <row r="329" ht="16.5" customHeight="1" s="26">
       <c r="J329" s="9" t="inlineStr">
@@ -15821,6 +16320,7 @@
         </is>
       </c>
       <c r="AB329" t="inlineStr"/>
+      <c r="AC329" t="inlineStr"/>
     </row>
     <row r="330" ht="33" customHeight="1" s="26">
       <c r="J330" s="9" t="inlineStr">
@@ -15866,9 +16366,10 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>数据示例'附件1.excel'不符合域类型'an..(50)'的限制: 包含汉字字符'附'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'附件1.excel'不符合域类型'an..(50)'的限制: 包含汉字字符'附'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC330" t="inlineStr"/>
     </row>
     <row r="331" ht="33" customHeight="1" s="26">
       <c r="J331" s="9" t="inlineStr">
@@ -15913,6 +16414,11 @@
         </is>
       </c>
       <c r="AB331" t="inlineStr"/>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>因为字段为上传人，指上传文件的经办人员，通常存储的是人员姓名，属于说明描述类信息，应为文本类；而编码类指具有特定编码规则的符号如工号等，此处并非编码含义，故填写编码类可能错误。，当前字段所属类型可能错误，应为文本类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="33" customHeight="1" s="26">
       <c r="J332" s="9" t="inlineStr">
@@ -15955,6 +16461,7 @@
         </is>
       </c>
       <c r="AB332" t="inlineStr"/>
+      <c r="AC332" t="inlineStr"/>
     </row>
     <row r="333" ht="33" customHeight="1" s="26">
       <c r="J333" s="9" t="inlineStr">
@@ -15989,7 +16496,7 @@
       </c>
       <c r="W333" s="9" t="inlineStr">
         <is>
-          <t>01-成功;02-失败</t>
+          <t>成功、失败</t>
         </is>
       </c>
       <c r="Y333" s="9" t="inlineStr">
@@ -15999,10 +16506,15 @@
       </c>
       <c r="AA333" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB333" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>1. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC333" t="inlineStr"/>
     </row>
     <row r="334" ht="16.5" customHeight="1" s="26">
       <c r="J334" s="9" t="inlineStr">
@@ -16048,9 +16560,10 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>数据示例'已确认事项类型'不符合域类型'an..(20)'的限制: 包含汉字字符'已'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'已确认事项类型'不符合域类型'an..(20)'的限制: 包含汉字字符'已'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC334" t="inlineStr"/>
     </row>
     <row r="335" ht="16.5" customHeight="1" s="26">
       <c r="J335" s="9" t="inlineStr">
@@ -16095,6 +16608,11 @@
         </is>
       </c>
       <c r="AB335" t="inlineStr"/>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>因为字段为协商人员，指负责协商案件的人员，通常存储的是人员姓名，属于说明描述类信息，应为文本类；编码类适用于有特定编码规则的编号，与人员姓名含义不符，故填写编码类可能错误。，当前字段所属类型可能错误，应为文本类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="16.5" customHeight="1" s="26">
       <c r="J336" s="9" t="inlineStr">
@@ -16139,6 +16657,7 @@
         </is>
       </c>
       <c r="AB336" t="inlineStr"/>
+      <c r="AC336" t="inlineStr"/>
     </row>
     <row r="337" ht="16.5" customHeight="1" s="26">
       <c r="J337" s="9" t="inlineStr">
@@ -16184,9 +16703,10 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>数据示例'分类代码含义'不符合域类型'an..(30)'的限制: 包含汉字字符'分'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'分类代码含义'不符合域类型'an..(30)'的限制: 包含汉字字符'分'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr"/>
     </row>
     <row r="338" ht="16.5" customHeight="1" s="26">
       <c r="J338" s="9" t="inlineStr">
@@ -16232,9 +16752,10 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>数据示例'红色'不符合域类型'an..(10)'的限制: 包含汉字字符'红'（数字+字母+特殊符号类不允许汉字）</t>
-        </is>
-      </c>
+          <t>1. 数据示例'红色'不符合域类型'an..(10)'的限制: 包含汉字字符'红'（数字+字母+特殊符号类不允许汉字）</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr"/>
     </row>
     <row r="339" ht="16.5" customHeight="1" s="26">
       <c r="J339" s="9" t="inlineStr">
@@ -16280,9 +16801,10 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>域类型'i(20)'不允许用于字段所属类型'文本类'</t>
-        </is>
-      </c>
+          <t>1. 域类型'i(20)'不允许用于字段所属类型'文本类'</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr"/>
     </row>
     <row r="340" ht="16.5" customHeight="1" s="26">
       <c r="J340" s="9" t="inlineStr">
@@ -16328,9 +16850,10 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>域类型'i(20)'不允许用于字段所属类型'文本类'</t>
-        </is>
-      </c>
+          <t>1. 域类型'i(20)'不允许用于字段所属类型'文本类'</t>
+        </is>
+      </c>
+      <c r="AC340" t="inlineStr"/>
     </row>
     <row r="341" ht="16.5" customHeight="1" s="26">
       <c r="J341" s="9" t="inlineStr">
@@ -16375,6 +16898,7 @@
         </is>
       </c>
       <c r="AB341" t="inlineStr"/>
+      <c r="AC341" t="inlineStr"/>
     </row>
     <row r="342" ht="16.5" customHeight="1" s="26">
       <c r="J342" s="9" t="inlineStr">
@@ -16419,6 +16943,11 @@
         </is>
       </c>
       <c r="AB342" t="inlineStr"/>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>因为"前Scenario"存储的是变更前Scenario ID（当前催收场景号），是用于标识催收场景的编号/代码，具有特定编码规则，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="16.5" customHeight="1" s="26">
       <c r="J343" s="9" t="inlineStr">
@@ -16463,6 +16992,11 @@
         </is>
       </c>
       <c r="AB343" t="inlineStr"/>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>因为"前Collection"存储的是变更前Collection ID（当前催收场景的行动号），是标识催收行动编号的代码，具有特定编码规则，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="16.5" customHeight="1" s="26">
       <c r="J344" s="9" t="inlineStr">
@@ -16507,6 +17041,11 @@
         </is>
       </c>
       <c r="AB344" t="inlineStr"/>
+      <c r="AC344" t="inlineStr">
+        <is>
+          <t>因为"新Scenario"存储的是新Scenario ID，是标识催收场景的编号代码，具有特定编码规则，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="345" ht="16.5" customHeight="1" s="26">
       <c r="J345" s="9" t="inlineStr">
@@ -16551,6 +17090,11 @@
         </is>
       </c>
       <c r="AB345" t="inlineStr"/>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>因为"新Collection"存储的是新Collection ID，是标识催收行动编号的代码，具有特定编码规则，应属于编码类，而非文本类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="16.5" customHeight="1" s="26">
       <c r="J346" s="9" t="inlineStr">
@@ -16593,6 +17137,7 @@
         </is>
       </c>
       <c r="AB346" t="inlineStr"/>
+      <c r="AC346" t="inlineStr"/>
     </row>
     <row r="347" ht="99" customHeight="1" s="26">
       <c r="J347" s="9" t="inlineStr">
@@ -16638,9 +17183,10 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>域类型'an(1)'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 标志类字段的'是否枚举'必须为'是'，实际为'否'</t>
+        </is>
+      </c>
+      <c r="AC347" t="inlineStr"/>
     </row>
     <row r="348" ht="66" customHeight="1" s="26">
       <c r="J348" s="9" t="inlineStr">
@@ -16686,9 +17232,10 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>域类型'an..(1)'不允许用于字段所属类型'标志类'</t>
-        </is>
-      </c>
+          <t>1. 标志类字段的'是否枚举'必须为'是'，实际为'否'</t>
+        </is>
+      </c>
+      <c r="AC348" t="inlineStr"/>
     </row>
     <row r="349" ht="16.5" customHeight="1" s="26">
       <c r="J349" s="9" t="inlineStr">
@@ -16723,7 +17270,7 @@
       </c>
       <c r="W349" s="9" t="inlineStr">
         <is>
-          <t>01-是;02-否</t>
+          <t>是、否</t>
         </is>
       </c>
       <c r="Y349" s="9" t="inlineStr">
@@ -16738,9 +17285,11 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>字段中文名'用卡判断标识'不属于见名知意的常见金融名称，业务含义'案件客户用卡判断的标识'只是在原名称基础上添加了'案件客户'和'的'，语义上与字段名完全等价，未解释该标识的具体含义、取值或用途，属于简单加词/语义重复，判定为无效。</t>
-        </is>
-      </c>
+          <t>1. 字段中文名'用卡判断标识'不属于见名知意的常见名称，而业务含义'案件客户用卡判断的标识'只是在原名称基础上增加了'案件客户'和'的'等限定修饰，语义上与字段名基本等价，没有解释'用卡判断'的具体含义、取值或业务背景，未提供实质信息，属于语义重复，判定为无效。
+2. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC349" t="inlineStr"/>
     </row>
     <row r="350" ht="33" customHeight="1" s="26">
       <c r="J350" s="9" t="inlineStr">
@@ -16785,6 +17334,11 @@
         </is>
       </c>
       <c r="AB350" t="inlineStr"/>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>因为该字段值为0005时显示"躲避"、0006时显示"失联"、其他值显示空白，本质是对缺失关联客户类型/状态的枚举分类取值，属于代码枚举类；虽然值采用编码形式，但其含义是分类状态，应属于代码枚举类而非编码类。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="351" ht="16.5" customHeight="1" s="26">
       <c r="J351" s="9" t="inlineStr">
@@ -16829,6 +17383,11 @@
         </is>
       </c>
       <c r="AB351" t="inlineStr"/>
+      <c r="AC351" t="inlineStr">
+        <is>
+          <t>因为"账户状态字"记录的是核心主机系统中的账户状态，状态属于明确的分类取值（类型、状态、种类、模式），应属于代码枚举类，而非编码类。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="49.5" customHeight="1" s="26">
       <c r="J352" s="9" t="inlineStr">
@@ -16873,6 +17432,11 @@
         </is>
       </c>
       <c r="AB352" t="inlineStr"/>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>因为该字段根据投诉次数合计是否&gt;=1输出"是"，反之输出空白（即否），取值只有"是"和"否"两种，属于标志类，而非编码类。，当前字段所属类型可能错误，应为标志类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="353" ht="33" customHeight="1" s="26">
       <c r="J353" s="9" t="inlineStr">
@@ -16917,6 +17481,11 @@
         </is>
       </c>
       <c r="AB353" t="inlineStr"/>
+      <c r="AC353" t="inlineStr">
+        <is>
+          <t>因为业务定义为“近1年外部投诉总次数&gt;=1则输出是，反之则为空”，字段取值只有“是”和空两种，即属于只有“是/否”两种取值的标志类字段。填写为编码类不正确，应为标志类。，当前字段所属类型可能错误，应为标志类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="49.5" customHeight="1" s="26">
       <c r="J354" s="9" t="inlineStr">
@@ -16961,6 +17530,11 @@
         </is>
       </c>
       <c r="AB354" t="inlineStr"/>
+      <c r="AC354" t="inlineStr">
+        <is>
+          <t>因为业务定义中司法标识取值为“待司法”和“未司法”两种状态，属于有明确分类取值的状态指示字段，应为代码枚举类。编码类应指具有特定编码规则的数据项（如证件号码、机构代码），此处不符合，故填写错误。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="355" ht="16.5" customHeight="1" s="26">
       <c r="J355" s="9" t="inlineStr">
@@ -17005,6 +17579,11 @@
         </is>
       </c>
       <c r="AB355" t="inlineStr"/>
+      <c r="AC355" t="inlineStr">
+        <is>
+          <t>因为分行协作人员记录的是总分行间配置的协作人员，属于人员姓名等说明描述类信息，应为文本类。编码类要求数据具有特定编码规则，此处不满足，填写为编码类错误。，当前字段所属类型可能错误，应为文本类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="16.5" customHeight="1" s="26">
       <c r="J356" s="9" t="inlineStr">
@@ -17050,9 +17629,10 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>域类型'i(18,2)'不允许用于字段所属类型'编码类'</t>
-        </is>
-      </c>
+          <t>1. 域类型'i(18,2)'不允许用于字段所属类型'编码类'</t>
+        </is>
+      </c>
+      <c r="AC356" t="inlineStr"/>
     </row>
     <row r="357" ht="33" customHeight="1" s="26">
       <c r="J357" s="9" t="inlineStr">
@@ -17097,6 +17677,7 @@
         </is>
       </c>
       <c r="AB357" t="inlineStr"/>
+      <c r="AC357" t="inlineStr"/>
     </row>
     <row r="358" ht="33" customHeight="1" s="26">
       <c r="J358" s="9" t="inlineStr">
@@ -17139,6 +17720,7 @@
         </is>
       </c>
       <c r="AB358" t="inlineStr"/>
+      <c r="AC358" t="inlineStr"/>
     </row>
     <row r="359" ht="16.5" customHeight="1" s="26">
       <c r="J359" s="9" t="inlineStr">
@@ -17173,7 +17755,7 @@
       </c>
       <c r="W359" s="9" t="inlineStr">
         <is>
-          <t>01-高;02-中;03-低;04-空</t>
+          <t>高、中、低、空</t>
         </is>
       </c>
       <c r="Y359" s="9" t="inlineStr">
@@ -17183,10 +17765,15 @@
       </c>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB359" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB359" t="inlineStr">
+        <is>
+          <t>1. 枚举值缺少代码，应填写'代码-码值'形式</t>
+        </is>
+      </c>
+      <c r="AC359" t="inlineStr"/>
     </row>
     <row r="360" ht="49.5" customHeight="1" s="26">
       <c r="J360" s="9" t="inlineStr">
@@ -17231,6 +17818,7 @@
         </is>
       </c>
       <c r="AB360" t="inlineStr"/>
+      <c r="AC360" t="inlineStr"/>
     </row>
     <row r="361" ht="49.5" customHeight="1" s="26">
       <c r="J361" s="9" t="inlineStr">
@@ -17275,6 +17863,7 @@
         </is>
       </c>
       <c r="AB361" t="inlineStr"/>
+      <c r="AC361" t="inlineStr"/>
     </row>
     <row r="362" ht="33" customHeight="1" s="26">
       <c r="J362" s="9" t="inlineStr">
@@ -17319,6 +17908,7 @@
         </is>
       </c>
       <c r="AB362" t="inlineStr"/>
+      <c r="AC362" t="inlineStr"/>
     </row>
     <row r="363" ht="33" customHeight="1" s="26">
       <c r="J363" s="9" t="inlineStr">
@@ -17363,6 +17953,7 @@
         </is>
       </c>
       <c r="AB363" t="inlineStr"/>
+      <c r="AC363" t="inlineStr"/>
     </row>
     <row r="364" ht="16.5" customHeight="1" s="26">
       <c r="J364" s="9" t="inlineStr">
@@ -17407,6 +17998,11 @@
         </is>
       </c>
       <c r="AB364" t="inlineStr"/>
+      <c r="AC364" t="inlineStr">
+        <is>
+          <t>因为消息推送方表示消息推送的来源方，默认值为“系统”，通常为有限的固定取值（如系统、人工等），属于有明确分类取值的代码枚举类字段，而非文本类。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="16.5" customHeight="1" s="26">
       <c r="J365" s="9" t="inlineStr">
@@ -17451,6 +18047,7 @@
         </is>
       </c>
       <c r="AB365" t="inlineStr"/>
+      <c r="AC365" t="inlineStr"/>
     </row>
     <row r="366" ht="16.5" customHeight="1" s="26">
       <c r="J366" s="9" t="inlineStr">
@@ -17495,6 +18092,7 @@
         </is>
       </c>
       <c r="AB366" t="inlineStr"/>
+      <c r="AC366" t="inlineStr"/>
     </row>
     <row r="367" ht="49.5" customHeight="1" s="26">
       <c r="J367" s="9" t="inlineStr">
@@ -17540,9 +18138,10 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>数据示例'您的案件（具体案件号）客户姓名：（案件对应的客户姓名）有约联待处理。'不符合域类型'anc..(20)'的限制: 长度超过最大限制20位，实际34位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'您的案件（具体案件号）客户姓名：（案件对应的客户姓名）有约联待处理。'不符合域类型'anc..(20)'的限制: 长度超过最大限制20位，实际34位</t>
+        </is>
+      </c>
+      <c r="AC367" t="inlineStr"/>
     </row>
     <row r="368" ht="16.5" customHeight="1" s="26">
       <c r="J368" s="9" t="inlineStr">
@@ -17587,6 +18186,7 @@
         </is>
       </c>
       <c r="AB368" t="inlineStr"/>
+      <c r="AC368" t="inlineStr"/>
     </row>
     <row r="369" ht="16.5" customHeight="1" s="26">
       <c r="J369" s="15" t="inlineStr">
@@ -17632,9 +18232,10 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>数据示例'10'不符合域类型'n!(20)'的限制: 长度应为20位，实际2位</t>
-        </is>
-      </c>
+          <t>1. 数据示例'10'不符合域类型'n!(20)'的限制: 长度应为20位，实际2位</t>
+        </is>
+      </c>
+      <c r="AC369" t="inlineStr"/>
     </row>
     <row r="370" ht="16.5" customHeight="1" s="26">
       <c r="J370" s="15" t="inlineStr">
@@ -17679,6 +18280,7 @@
         </is>
       </c>
       <c r="AB370" t="inlineStr"/>
+      <c r="AC370" t="inlineStr"/>
     </row>
     <row r="371" ht="16.5" customHeight="1" s="26">
       <c r="J371" s="15" t="inlineStr">
@@ -17724,9 +18326,10 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>域类型'text'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'text'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC371" t="inlineStr"/>
     </row>
     <row r="372" ht="16.5" customHeight="1" s="26">
       <c r="J372" s="15" t="inlineStr">
@@ -17771,6 +18374,11 @@
         </is>
       </c>
       <c r="AB372" t="inlineStr"/>
+      <c r="AC372" t="inlineStr">
+        <is>
+          <t>因为名称字段用于表示配置Id对应的名称，名称属于描述性文字信息，应为文本类；填写为编码类不恰当，编码类适用于证件号码、机构代码等具有特定编码规则的标识符，而名称不具备编码规则。，当前字段所属类型可能错误，应为文本类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="373" ht="16.5" customHeight="1" s="26">
       <c r="J373" s="15" t="inlineStr">
@@ -17813,6 +18421,7 @@
         </is>
       </c>
       <c r="AB373" t="inlineStr"/>
+      <c r="AC373" t="inlineStr"/>
     </row>
     <row r="374" ht="16.5" customHeight="1" s="26">
       <c r="J374" s="15" t="inlineStr">
@@ -17855,6 +18464,7 @@
         </is>
       </c>
       <c r="AB374" t="inlineStr"/>
+      <c r="AC374" t="inlineStr"/>
     </row>
     <row r="375" ht="16.5" customHeight="1" s="26">
       <c r="J375" s="15" t="inlineStr">
@@ -17899,6 +18509,7 @@
         </is>
       </c>
       <c r="AB375" t="inlineStr"/>
+      <c r="AC375" t="inlineStr"/>
     </row>
     <row r="376" ht="33" customHeight="1" s="26">
       <c r="J376" s="9" t="inlineStr">
@@ -17951,6 +18562,7 @@
         </is>
       </c>
       <c r="AB376" t="inlineStr"/>
+      <c r="AC376" t="inlineStr"/>
     </row>
     <row r="377" ht="16.5" customHeight="1" s="26">
       <c r="J377" s="15" t="inlineStr">
@@ -17995,6 +18607,11 @@
         </is>
       </c>
       <c r="AB377" t="inlineStr"/>
+      <c r="AC377" t="inlineStr">
+        <is>
+          <t>因为分数是这条策略对应的得分，属于数量/得分信息，应以数值形式存储和比较，应为数值类；填写为编码类不恰当，编码类适用于具有特定编码规则的标识符，而分数是数值型度量结果。，当前字段所属类型可能错误，应为数值类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="378" ht="33" customHeight="1" s="26">
       <c r="J378" s="15" t="inlineStr">
@@ -18035,10 +18652,15 @@
       </c>
       <c r="AA378" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB378" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB378" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'命中策略'与业务含义'命中的策略'语义完全等价，业务含义只是在原名称基础上加了'的'字，没有提供任何字段名之外的新信息，属于简单加词/语义重复，且'命中策略'并非日常通用名称，判定无效。</t>
+        </is>
+      </c>
+      <c r="AC378" t="inlineStr"/>
     </row>
     <row r="379" ht="33" customHeight="1" s="26">
       <c r="J379" s="15" t="inlineStr">
@@ -18079,10 +18701,15 @@
       </c>
       <c r="AA379" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB379" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB379" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'未命中策略'与业务含义'未命中策略'完全相同，属于完全复制，业务含义未对字段做任何解释或补充信息。'未命中策略'是需要领域背景的术语，不算见名知意，因此无效。</t>
+        </is>
+      </c>
+      <c r="AC379" t="inlineStr"/>
     </row>
     <row r="380" ht="33" customHeight="1" s="26">
       <c r="J380" s="15" t="inlineStr">
@@ -18123,10 +18750,15 @@
       </c>
       <c r="AA380" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB380" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'评分细则'与业务含义'评分细则'完全相同，属于完全复制，未提供任何解释性信息。'评分细则'虽有一定可读性，但不属于客户名称这类日常通用名称，业务含义未添加实质内容，判定无效。</t>
+        </is>
+      </c>
+      <c r="AC380" t="inlineStr"/>
     </row>
     <row r="381" ht="16.5" customHeight="1" s="26">
       <c r="J381" s="15" t="inlineStr">
@@ -18171,6 +18803,11 @@
         </is>
       </c>
       <c r="AB381" t="inlineStr"/>
+      <c r="AC381" t="inlineStr">
+        <is>
+          <t>因为字段为'状态'，指对话进行的状态，属于有明确分类、多取值的状态信息（如进行中、已完成等），应属于代码枚举类。而填写为'编码类'，编码类指具有特定编码规则的符号（如证件号码、机构代码），状态并不具有编码规则，因此现有类型不符合，应为代码枚举类。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="16.5" customHeight="1" s="26">
       <c r="J382" s="15" t="inlineStr">
@@ -18215,6 +18852,7 @@
         </is>
       </c>
       <c r="AB382" t="inlineStr"/>
+      <c r="AC382" t="inlineStr"/>
     </row>
     <row r="383" ht="16.5" customHeight="1" s="26">
       <c r="J383" s="15" t="inlineStr">
@@ -18259,6 +18897,11 @@
         </is>
       </c>
       <c r="AB383" t="inlineStr"/>
+      <c r="AC383" t="inlineStr">
+        <is>
+          <t>因为字段'时间间隔'指两次对话的时间间隔，是一个时长/数量信息（如秒数、分钟数），应属于数值类。而填写为'文本类'，文本类适用于说明描述类信息，时间间隔并非描述性文字，因此现有类型不符合，应为数值类。，当前字段所属类型可能错误，应为数值类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="16.5" customHeight="1" s="26">
       <c r="J384" s="15" t="inlineStr">
@@ -18303,6 +18946,11 @@
         </is>
       </c>
       <c r="AB384" t="inlineStr"/>
+      <c r="AC384" t="inlineStr">
+        <is>
+          <t>因为字段'场景'指对话应用的场景，场景属于有明确分类、多取值的枚举信息（如不同业务场景），应属于代码枚举类。而填写为'文本类'，文本类适用于说明描述类信息，场景是分类属性而非描述文字，因此现有类型不符合，应为代码枚举类。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="385" ht="16.5" customHeight="1" s="26">
       <c r="J385" s="15" t="inlineStr">
@@ -18343,10 +18991,15 @@
       </c>
       <c r="AA385" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB385" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB385" t="inlineStr">
+        <is>
+          <t>1. 标志类字段的'是否枚举'必须为'是'，实际为'否'</t>
+        </is>
+      </c>
+      <c r="AC385" t="inlineStr"/>
     </row>
     <row r="386" ht="16.5" customHeight="1" s="26">
       <c r="J386" s="15" t="inlineStr">
@@ -18387,10 +19040,15 @@
       </c>
       <c r="AA386" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB386" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'策略名称'与业务含义'每种策略的名称'在语义上完全等价，'每种'只是对复数的修饰，并未增加任何字段名之外的信息，属于语义重复换说法，判定无效。</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr"/>
     </row>
     <row r="387" ht="33" customHeight="1" s="26">
       <c r="J387" s="15" t="inlineStr">
@@ -18435,6 +19093,7 @@
         </is>
       </c>
       <c r="AB387" t="inlineStr"/>
+      <c r="AC387" t="inlineStr"/>
     </row>
     <row r="388" ht="16.5" customHeight="1" s="26">
       <c r="J388" s="15" t="inlineStr">
@@ -18479,6 +19138,7 @@
         </is>
       </c>
       <c r="AB388" t="inlineStr"/>
+      <c r="AC388" t="inlineStr"/>
     </row>
     <row r="389" ht="16.5" customHeight="1" s="26">
       <c r="J389" s="15" t="inlineStr">
@@ -18521,6 +19181,7 @@
         </is>
       </c>
       <c r="AB389" t="inlineStr"/>
+      <c r="AC389" t="inlineStr"/>
     </row>
     <row r="390" ht="16.5" customHeight="1" s="26">
       <c r="J390" s="15" t="inlineStr">
@@ -18565,6 +19226,7 @@
         </is>
       </c>
       <c r="AB390" t="inlineStr"/>
+      <c r="AC390" t="inlineStr"/>
     </row>
     <row r="391" ht="16.5" customHeight="1" s="26">
       <c r="J391" s="15" t="inlineStr">
@@ -18609,6 +19271,7 @@
         </is>
       </c>
       <c r="AB391" t="inlineStr"/>
+      <c r="AC391" t="inlineStr"/>
     </row>
     <row r="392" ht="16.5" customHeight="1" s="26">
       <c r="J392" s="15" t="inlineStr">
@@ -18649,10 +19312,15 @@
       </c>
       <c r="AA392" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB392" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB392" t="inlineStr">
+        <is>
+          <t>1. 字段中文名'推荐度'应指推荐的程度或分值，而业务含义'在不同场景推荐使用什么策略'描述的是推荐策略的选择逻辑，并非对'推荐度'这一字段含义的解释，两者语义不匹配，业务含义与字段名不相关，因此无效。</t>
+        </is>
+      </c>
+      <c r="AC392" t="inlineStr"/>
     </row>
     <row r="393" ht="33" customHeight="1" s="26">
       <c r="J393" s="15" t="inlineStr">
@@ -18697,6 +19365,7 @@
         </is>
       </c>
       <c r="AB393" t="inlineStr"/>
+      <c r="AC393" t="inlineStr"/>
     </row>
     <row r="394" ht="33" customHeight="1" s="26">
       <c r="J394" s="15" t="inlineStr">
@@ -18741,6 +19410,11 @@
         </is>
       </c>
       <c r="AB394" t="inlineStr"/>
+      <c r="AC394" t="inlineStr">
+        <is>
+          <t>因为字段名为“角色”，业务定义为“扮演了什么类型的角色”，表明该字段描述的是角色类型，存在多种固定取值（如管理员、普通用户等），属于明确分类/多取值的枚举型数据，应归为代码枚举类。填写为文本类不准确。，当前字段所属类型可能错误，应为代码枚举类，请联系业务确认</t>
+        </is>
+      </c>
     </row>
     <row r="395" ht="33" customHeight="1" s="26">
       <c r="J395" s="9" t="inlineStr">
@@ -18785,6 +19459,7 @@
         </is>
       </c>
       <c r="AB395" t="inlineStr"/>
+      <c r="AC395" t="inlineStr"/>
     </row>
     <row r="396" ht="33" customHeight="1" s="26">
       <c r="J396" s="9" t="inlineStr">
@@ -18829,6 +19504,7 @@
         </is>
       </c>
       <c r="AB396" t="inlineStr"/>
+      <c r="AC396" t="inlineStr"/>
     </row>
     <row r="397" ht="33" customHeight="1" s="26">
       <c r="J397" s="9" t="inlineStr">
@@ -18869,10 +19545,15 @@
       </c>
       <c r="AA397" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB397" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB397" t="inlineStr">
+        <is>
+          <t>1. 标志类字段的'是否枚举'必须为'是'，实际为'否'</t>
+        </is>
+      </c>
+      <c r="AC397" t="inlineStr"/>
     </row>
     <row r="398" ht="33" customHeight="1" s="26">
       <c r="J398" s="9" t="inlineStr">
@@ -18913,10 +19594,16 @@
       </c>
       <c r="AA398" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB398" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB398" t="inlineStr">
+        <is>
+          <t>1. 标志类字段的'是否枚举'必须为'是'，实际为'否'
+2. 字段中文名'不安全或违法'与业务含义'判断对话是否安全或者合法'在语义上完全等价：'不安全'对应'是否安全'（否定关系），'违法'对应'是否合法'（否定关系）。业务含义只是将字段中文名换了一种说法并加上'判断对话'这一简单引导语，未提供任何字段名之外的实质信息，属于语义重复，因此判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC398" t="inlineStr"/>
     </row>
     <row r="399" ht="33" customHeight="1" s="26">
       <c r="J399" s="9" t="inlineStr">
@@ -18957,10 +19644,15 @@
       </c>
       <c r="AA399" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB399" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB399" t="inlineStr">
+        <is>
+          <t>1. 标志类字段的'是否枚举'必须为'是'，实际为'否'</t>
+        </is>
+      </c>
+      <c r="AC399" t="inlineStr"/>
     </row>
     <row r="400" ht="33" customHeight="1" s="26">
       <c r="J400" s="9" t="inlineStr">
@@ -19001,10 +19693,16 @@
       </c>
       <c r="AA400" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="AB400" t="inlineStr"/>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="AB400" t="inlineStr">
+        <is>
+          <t>1. 标志类字段的'是否枚举'必须为'是'，实际为'否'
+2. 字段中文名'重复对话'本身已能明确表达'重复出现的对话'这一含义，而业务含义'判断是否是重复对话'只是在原名称基础上添加了'判断是否是'这一无实质意义的动词短语，语义上与字段名完全等价，未提供任何额外信息，属于简单加词/语义重复，因此判定为无效。</t>
+        </is>
+      </c>
+      <c r="AC400" t="inlineStr"/>
     </row>
     <row r="401" ht="33" customHeight="1" s="26">
       <c r="J401" s="9" t="inlineStr">
@@ -19050,14 +19748,15 @@
       </c>
       <c r="AB401" t="inlineStr">
         <is>
-          <t>域类型'anc()'格式不合法</t>
-        </is>
-      </c>
+          <t>1. 域类型'anc()'格式不合法</t>
+        </is>
+      </c>
+      <c r="AC401" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:AB401"/>
   <mergeCells count="3">
-    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="I1:Z1"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
